--- a/infant_retinal_database_info.xlsx
+++ b/infant_retinal_database_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artemis\ARG@CS.FEI.VSB Dropbox\Jana Nowakova\03 CLANKY\Dataset - retiny\images_from_doctor\ARTICLE_dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8939A45E-E657-4D7D-9EB7-28286CFD8A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8485CE69-FF9C-4751-AE9C-0952B4D7A05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="38505" windowHeight="23400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="database" sheetId="7" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">database!$A$1:$I$485</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -367,9 +367,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -401,6 +398,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -429,9 +429,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 –⁠ 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -469,7 +469,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 –⁠ 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -575,7 +575,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 –⁠ 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -717,7 +717,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -743,36 +743,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="22">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -801,7 +801,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -830,7 +830,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+      <c r="A4" s="21">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -859,7 +859,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+      <c r="A5" s="21">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -888,7 +888,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
+      <c r="A6" s="21">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -901,7 +901,7 @@
         <v>4040</v>
       </c>
       <c r="E6" s="7">
-        <v>43.285714285714285</v>
+        <v>43</v>
       </c>
       <c r="F6" s="12">
         <v>11</v>
@@ -917,7 +917,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -930,7 +930,7 @@
         <v>4040</v>
       </c>
       <c r="E7" s="7">
-        <v>45.285714285714285</v>
+        <v>45</v>
       </c>
       <c r="F7" s="12">
         <v>11</v>
@@ -946,7 +946,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+      <c r="A8" s="21">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -959,7 +959,7 @@
         <v>3950</v>
       </c>
       <c r="E8" s="7">
-        <v>42.285714285714299</v>
+        <v>42</v>
       </c>
       <c r="F8" s="12">
         <v>11</v>
@@ -975,7 +975,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+      <c r="A9" s="21">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -988,7 +988,7 @@
         <v>3950</v>
       </c>
       <c r="E9" s="7">
-        <v>55.571428571428598</v>
+        <v>56</v>
       </c>
       <c r="F9" s="12">
         <v>11</v>
@@ -1004,7 +1004,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1017,7 +1017,7 @@
         <v>3760</v>
       </c>
       <c r="E10" s="7">
-        <v>42.142857142857146</v>
+        <v>42</v>
       </c>
       <c r="F10" s="12">
         <v>11</v>
@@ -1033,7 +1033,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1046,7 +1046,7 @@
         <v>3760</v>
       </c>
       <c r="E11" s="7">
-        <v>45.428571428571402</v>
+        <v>45</v>
       </c>
       <c r="F11" s="12">
         <v>11</v>
@@ -1062,7 +1062,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+      <c r="A12" s="21">
         <v>5</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1075,7 +1075,7 @@
         <v>3400</v>
       </c>
       <c r="E12" s="7">
-        <v>44.571428571428569</v>
+        <v>45</v>
       </c>
       <c r="F12" s="12">
         <v>11</v>
@@ -1091,7 +1091,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
+      <c r="A13" s="21">
         <v>5</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1104,7 +1104,7 @@
         <v>3400</v>
       </c>
       <c r="E13" s="7">
-        <v>48.428571428571431</v>
+        <v>48</v>
       </c>
       <c r="F13" s="12">
         <v>11</v>
@@ -1120,7 +1120,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="21">
         <v>5</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1133,7 +1133,7 @@
         <v>3400</v>
       </c>
       <c r="E14" s="7">
-        <v>52.428571428571431</v>
+        <v>52</v>
       </c>
       <c r="F14" s="12">
         <v>11</v>
@@ -1149,7 +1149,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+      <c r="A15" s="21">
         <v>6</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -1178,7 +1178,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+      <c r="A16" s="21">
         <v>6</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -1207,7 +1207,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+      <c r="A17" s="21">
         <v>6</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -1220,7 +1220,7 @@
         <v>3200</v>
       </c>
       <c r="E17" s="7">
-        <v>53.285714285714285</v>
+        <v>53</v>
       </c>
       <c r="F17" s="12">
         <v>11</v>
@@ -1236,7 +1236,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="22">
+      <c r="A18" s="21">
         <v>7</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -1249,7 +1249,7 @@
         <v>950</v>
       </c>
       <c r="E18" s="7">
-        <v>33.142857142857146</v>
+        <v>33</v>
       </c>
       <c r="F18" s="12">
         <v>11</v>
@@ -1265,7 +1265,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="22">
+      <c r="A19" s="21">
         <v>7</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -1278,7 +1278,7 @@
         <v>950</v>
       </c>
       <c r="E19" s="7">
-        <v>35.142857142857146</v>
+        <v>35</v>
       </c>
       <c r="F19" s="12">
         <v>11</v>
@@ -1294,7 +1294,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="22">
+      <c r="A20" s="21">
         <v>7</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -1307,7 +1307,7 @@
         <v>950</v>
       </c>
       <c r="E20" s="7">
-        <v>37.142857142857146</v>
+        <v>37</v>
       </c>
       <c r="F20" s="12">
         <v>11</v>
@@ -1323,7 +1323,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="22">
+      <c r="A21" s="21">
         <v>7</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -1336,7 +1336,7 @@
         <v>950</v>
       </c>
       <c r="E21" s="7">
-        <v>39.428571428571431</v>
+        <v>39</v>
       </c>
       <c r="F21" s="12">
         <v>11</v>
@@ -1352,7 +1352,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="22">
+      <c r="A22" s="21">
         <v>7</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -1365,7 +1365,7 @@
         <v>950</v>
       </c>
       <c r="E22" s="7">
-        <v>43.428571428571431</v>
+        <v>43</v>
       </c>
       <c r="F22" s="12">
         <v>11</v>
@@ -1381,7 +1381,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="22">
+      <c r="A23" s="21">
         <v>7</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -1394,7 +1394,7 @@
         <v>950</v>
       </c>
       <c r="E23" s="7">
-        <v>49.428571428571431</v>
+        <v>49</v>
       </c>
       <c r="F23" s="12">
         <v>11</v>
@@ -1410,7 +1410,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="22">
+      <c r="A24" s="21">
         <v>8</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -1423,7 +1423,7 @@
         <v>2700</v>
       </c>
       <c r="E24" s="7">
-        <v>39.857142857142854</v>
+        <v>40</v>
       </c>
       <c r="F24" s="12">
         <v>11</v>
@@ -1439,7 +1439,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="22">
+      <c r="A25" s="21">
         <v>8</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -1452,7 +1452,7 @@
         <v>2700</v>
       </c>
       <c r="E25" s="7">
-        <v>41.142857142857146</v>
+        <v>41</v>
       </c>
       <c r="F25" s="12">
         <v>11</v>
@@ -1468,7 +1468,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="22">
+      <c r="A26" s="21">
         <v>8</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -1481,7 +1481,7 @@
         <v>2700</v>
       </c>
       <c r="E26" s="7">
-        <v>43.142857142857146</v>
+        <v>43</v>
       </c>
       <c r="F26" s="12">
         <v>11</v>
@@ -1497,7 +1497,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="22">
+      <c r="A27" s="21">
         <v>8</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -1510,7 +1510,7 @@
         <v>2700</v>
       </c>
       <c r="E27" s="7">
-        <v>47.142857142857139</v>
+        <v>47</v>
       </c>
       <c r="F27" s="12">
         <v>11</v>
@@ -1526,7 +1526,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="22">
+      <c r="A28" s="21">
         <v>9</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -1539,7 +1539,7 @@
         <v>2850</v>
       </c>
       <c r="E28" s="7">
-        <v>38.571428571428569</v>
+        <v>39</v>
       </c>
       <c r="F28" s="12">
         <v>11</v>
@@ -1555,7 +1555,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="22">
+      <c r="A29" s="21">
         <v>9</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -1568,7 +1568,7 @@
         <v>2850</v>
       </c>
       <c r="E29" s="7">
-        <v>41.571428571428569</v>
+        <v>42</v>
       </c>
       <c r="F29" s="12">
         <v>11</v>
@@ -1584,7 +1584,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="22">
+      <c r="A30" s="21">
         <v>10</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -1597,7 +1597,7 @@
         <v>3550</v>
       </c>
       <c r="E30" s="7">
-        <v>39.428571428571431</v>
+        <v>39</v>
       </c>
       <c r="F30" s="12">
         <v>11</v>
@@ -1613,7 +1613,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="22">
+      <c r="A31" s="21">
         <v>10</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -1626,7 +1626,7 @@
         <v>3550</v>
       </c>
       <c r="E31" s="7">
-        <v>44.714285714285715</v>
+        <v>45</v>
       </c>
       <c r="F31" s="12">
         <v>11</v>
@@ -1642,7 +1642,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="22">
+      <c r="A32" s="21">
         <v>10</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -1655,7 +1655,7 @@
         <v>3550</v>
       </c>
       <c r="E32" s="7">
-        <v>49.714285714285715</v>
+        <v>50</v>
       </c>
       <c r="F32" s="12">
         <v>11</v>
@@ -1671,7 +1671,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="22">
+      <c r="A33" s="21">
         <v>10</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -1684,7 +1684,7 @@
         <v>3550</v>
       </c>
       <c r="E33" s="7">
-        <v>52.571428571428569</v>
+        <v>53</v>
       </c>
       <c r="F33" s="12">
         <v>11</v>
@@ -1700,7 +1700,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="22">
+      <c r="A34" s="21">
         <v>10</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -1713,7 +1713,7 @@
         <v>3550</v>
       </c>
       <c r="E34" s="7">
-        <v>59.714285714285715</v>
+        <v>60</v>
       </c>
       <c r="F34" s="12">
         <v>11</v>
@@ -1729,7 +1729,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="22">
+      <c r="A35" s="21">
         <v>11</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -1742,7 +1742,7 @@
         <v>3510</v>
       </c>
       <c r="E35" s="7">
-        <v>72.428571428571431</v>
+        <v>72</v>
       </c>
       <c r="F35" s="6">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="22">
+      <c r="A36" s="21">
         <v>11</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -1771,7 +1771,7 @@
         <v>3510</v>
       </c>
       <c r="E36" s="7">
-        <v>89.428571428571431</v>
+        <v>89</v>
       </c>
       <c r="F36" s="6">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="22">
+      <c r="A37" s="21">
         <v>11</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -1800,7 +1800,7 @@
         <v>3510</v>
       </c>
       <c r="E37" s="7">
-        <v>113.42857142857143</v>
+        <v>113</v>
       </c>
       <c r="F37" s="6">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="22">
+      <c r="A38" s="21">
         <v>12</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -1845,7 +1845,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="22">
+      <c r="A39" s="21">
         <v>12</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -1858,7 +1858,7 @@
         <v>2210</v>
       </c>
       <c r="E39" s="7">
-        <v>41.285714285714285</v>
+        <v>41</v>
       </c>
       <c r="F39" s="12">
         <v>11</v>
@@ -1874,7 +1874,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="22">
+      <c r="A40" s="21">
         <v>13</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -1903,7 +1903,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="22">
+      <c r="A41" s="21">
         <v>13</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -1916,7 +1916,7 @@
         <v>3390</v>
       </c>
       <c r="E41" s="7">
-        <v>42.285714285714285</v>
+        <v>42</v>
       </c>
       <c r="F41" s="12">
         <v>11</v>
@@ -1932,7 +1932,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="22">
+      <c r="A42" s="21">
         <v>13</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -1945,7 +1945,7 @@
         <v>3390</v>
       </c>
       <c r="E42" s="7">
-        <v>45.285714285714285</v>
+        <v>45</v>
       </c>
       <c r="F42" s="12">
         <v>11</v>
@@ -1961,7 +1961,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="22">
+      <c r="A43" s="21">
         <v>14</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -1990,7 +1990,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="22">
+      <c r="A44" s="21">
         <v>14</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -2003,7 +2003,7 @@
         <v>3700</v>
       </c>
       <c r="E44" s="7">
-        <v>45.285714285714285</v>
+        <v>45</v>
       </c>
       <c r="F44" s="12">
         <v>11</v>
@@ -2019,7 +2019,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="22">
+      <c r="A45" s="21">
         <v>15</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -2048,7 +2048,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="22">
+      <c r="A46" s="21">
         <v>16</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -2061,7 +2061,7 @@
         <v>2960</v>
       </c>
       <c r="E46" s="7">
-        <v>36.285714285714285</v>
+        <v>36</v>
       </c>
       <c r="F46" s="12">
         <v>11</v>
@@ -2077,7 +2077,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="22">
+      <c r="A47" s="21">
         <v>16</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -2090,7 +2090,7 @@
         <v>2960</v>
       </c>
       <c r="E47" s="7">
-        <v>41.285714285714285</v>
+        <v>41</v>
       </c>
       <c r="F47" s="12">
         <v>11</v>
@@ -2106,7 +2106,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="22">
+      <c r="A48" s="21">
         <v>17</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -2119,7 +2119,7 @@
         <v>1660</v>
       </c>
       <c r="E48" s="7">
-        <v>33.142857142857146</v>
+        <v>33</v>
       </c>
       <c r="F48" s="12">
         <v>11</v>
@@ -2135,7 +2135,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="22">
+      <c r="A49" s="21">
         <v>17</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -2148,7 +2148,7 @@
         <v>1660</v>
       </c>
       <c r="E49" s="7">
-        <v>36.571428571428569</v>
+        <v>37</v>
       </c>
       <c r="F49" s="12">
         <v>11</v>
@@ -2164,7 +2164,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="22">
+      <c r="A50" s="21">
         <v>18</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -2177,7 +2177,7 @@
         <v>1390</v>
       </c>
       <c r="E50" s="7">
-        <v>36.857142857142854</v>
+        <v>37</v>
       </c>
       <c r="F50" s="12">
         <v>11</v>
@@ -2193,7 +2193,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="22">
+      <c r="A51" s="21">
         <v>19</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -2206,7 +2206,7 @@
         <v>3050</v>
       </c>
       <c r="E51" s="7">
-        <v>37.857142857142854</v>
+        <v>38</v>
       </c>
       <c r="F51" s="12">
         <v>11</v>
@@ -2222,7 +2222,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="22">
+      <c r="A52" s="21">
         <v>19</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -2235,7 +2235,7 @@
         <v>3050</v>
       </c>
       <c r="E52" s="7">
-        <v>40.857142857142854</v>
+        <v>41</v>
       </c>
       <c r="F52" s="12">
         <v>11</v>
@@ -2251,7 +2251,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="22">
+      <c r="A53" s="21">
         <v>19</v>
       </c>
       <c r="B53" s="6" t="s">
@@ -2264,7 +2264,7 @@
         <v>3050</v>
       </c>
       <c r="E53" s="7">
-        <v>45.857142857142861</v>
+        <v>46</v>
       </c>
       <c r="F53" s="12">
         <v>11</v>
@@ -2280,7 +2280,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="22">
+      <c r="A54" s="21">
         <v>19</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -2293,7 +2293,7 @@
         <v>3050</v>
       </c>
       <c r="E54" s="7">
-        <v>52.857142857142861</v>
+        <v>53</v>
       </c>
       <c r="F54" s="12">
         <v>11</v>
@@ -2309,7 +2309,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="22">
+      <c r="A55" s="21">
         <v>20</v>
       </c>
       <c r="B55" s="6" t="s">
@@ -2322,7 +2322,7 @@
         <v>3600</v>
       </c>
       <c r="E55" s="7">
-        <v>41.857142857142854</v>
+        <v>42</v>
       </c>
       <c r="F55" s="12">
         <v>11</v>
@@ -2338,7 +2338,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="22">
+      <c r="A56" s="21">
         <v>20</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -2351,7 +2351,7 @@
         <v>3600</v>
       </c>
       <c r="E56" s="7">
-        <v>46.857142857142854</v>
+        <v>47</v>
       </c>
       <c r="F56" s="12">
         <v>11</v>
@@ -2367,7 +2367,7 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="22">
+      <c r="A57" s="21">
         <v>20</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -2380,7 +2380,7 @@
         <v>3600</v>
       </c>
       <c r="E57" s="7">
-        <v>53.857142857142861</v>
+        <v>54</v>
       </c>
       <c r="F57" s="12">
         <v>11</v>
@@ -2396,7 +2396,7 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="22">
+      <c r="A58" s="21">
         <v>21</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -2409,7 +2409,7 @@
         <v>3670</v>
       </c>
       <c r="E58" s="7">
-        <v>41.571428571428569</v>
+        <v>42</v>
       </c>
       <c r="F58" s="12">
         <v>11</v>
@@ -2425,7 +2425,7 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="22">
+      <c r="A59" s="21">
         <v>21</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -2438,7 +2438,7 @@
         <v>3670</v>
       </c>
       <c r="E59" s="7">
-        <v>42.857142857142854</v>
+        <v>43</v>
       </c>
       <c r="F59" s="12">
         <v>11</v>
@@ -2454,7 +2454,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="22">
+      <c r="A60" s="21">
         <v>21</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -2467,7 +2467,7 @@
         <v>3670</v>
       </c>
       <c r="E60" s="7">
-        <v>46.857142857142854</v>
+        <v>47</v>
       </c>
       <c r="F60" s="12">
         <v>11</v>
@@ -2483,7 +2483,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="22">
+      <c r="A61" s="21">
         <v>22</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -2496,7 +2496,7 @@
         <v>3400</v>
       </c>
       <c r="E61" s="7">
-        <v>40.571428571428569</v>
+        <v>41</v>
       </c>
       <c r="F61" s="12">
         <v>11</v>
@@ -2512,7 +2512,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="22">
+      <c r="A62" s="21">
         <v>22</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -2525,7 +2525,7 @@
         <v>3400</v>
       </c>
       <c r="E62" s="7">
-        <v>43.857142857142854</v>
+        <v>44</v>
       </c>
       <c r="F62" s="12">
         <v>11</v>
@@ -2541,7 +2541,7 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="22">
+      <c r="A63" s="21">
         <v>23</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -2554,7 +2554,7 @@
         <v>3570</v>
       </c>
       <c r="E63" s="7">
-        <v>39.428571428571431</v>
+        <v>39</v>
       </c>
       <c r="F63" s="12">
         <v>11</v>
@@ -2570,7 +2570,7 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="22">
+      <c r="A64" s="21">
         <v>23</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -2583,7 +2583,7 @@
         <v>3570</v>
       </c>
       <c r="E64" s="7">
-        <v>42.857142857142854</v>
+        <v>43</v>
       </c>
       <c r="F64" s="12">
         <v>11</v>
@@ -2599,7 +2599,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="22">
+      <c r="A65" s="21">
         <v>24</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -2612,7 +2612,7 @@
         <v>3290</v>
       </c>
       <c r="E65" s="7">
-        <v>39.285714285714285</v>
+        <v>39</v>
       </c>
       <c r="F65" s="12">
         <v>11</v>
@@ -2628,7 +2628,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="22">
+      <c r="A66" s="21">
         <v>24</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -2641,7 +2641,7 @@
         <v>3290</v>
       </c>
       <c r="E66" s="7">
-        <v>43.571428571428569</v>
+        <v>44</v>
       </c>
       <c r="F66" s="12">
         <v>11</v>
@@ -2657,7 +2657,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="22">
+      <c r="A67" s="21">
         <v>25</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2670,7 +2670,7 @@
         <v>2370</v>
       </c>
       <c r="E67" s="7">
-        <v>36.285714285714285</v>
+        <v>36</v>
       </c>
       <c r="F67" s="12">
         <v>11</v>
@@ -2686,7 +2686,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="22">
+      <c r="A68" s="21">
         <v>25</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -2699,7 +2699,7 @@
         <v>2370</v>
       </c>
       <c r="E68" s="7">
-        <v>40.571428571428569</v>
+        <v>41</v>
       </c>
       <c r="F68" s="12">
         <v>11</v>
@@ -2715,7 +2715,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="22">
+      <c r="A69" s="21">
         <v>26</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -2728,7 +2728,7 @@
         <v>1700</v>
       </c>
       <c r="E69" s="7">
-        <v>34.142857142857146</v>
+        <v>34</v>
       </c>
       <c r="F69" s="12">
         <v>11</v>
@@ -2744,7 +2744,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="22">
+      <c r="A70" s="21">
         <v>26</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -2757,7 +2757,7 @@
         <v>1700</v>
       </c>
       <c r="E70" s="7">
-        <v>36.142857142857146</v>
+        <v>36</v>
       </c>
       <c r="F70" s="12">
         <v>11</v>
@@ -2773,7 +2773,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="22">
+      <c r="A71" s="21">
         <v>26</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -2786,7 +2786,7 @@
         <v>1700</v>
       </c>
       <c r="E71" s="7">
-        <v>38.142857142857146</v>
+        <v>38</v>
       </c>
       <c r="F71" s="12">
         <v>11</v>
@@ -2802,7 +2802,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="22">
+      <c r="A72" s="21">
         <v>26</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -2815,7 +2815,7 @@
         <v>1700</v>
       </c>
       <c r="E72" s="7">
-        <v>40.142857142857146</v>
+        <v>40</v>
       </c>
       <c r="F72" s="12">
         <v>11</v>
@@ -2831,7 +2831,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="22">
+      <c r="A73" s="21">
         <v>26</v>
       </c>
       <c r="B73" s="6" t="s">
@@ -2844,7 +2844,7 @@
         <v>1700</v>
       </c>
       <c r="E73" s="7">
-        <v>42.428571428571431</v>
+        <v>42</v>
       </c>
       <c r="F73" s="12">
         <v>11</v>
@@ -2860,7 +2860,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="22">
+      <c r="A74" s="21">
         <v>27</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -2873,7 +2873,7 @@
         <v>1460</v>
       </c>
       <c r="E74" s="7">
-        <v>32.571428571428569</v>
+        <v>33</v>
       </c>
       <c r="F74" s="12">
         <v>11</v>
@@ -2889,7 +2889,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="22">
+      <c r="A75" s="21">
         <v>27</v>
       </c>
       <c r="B75" s="6" t="s">
@@ -2902,7 +2902,7 @@
         <v>1460</v>
       </c>
       <c r="E75" s="7">
-        <v>34.571428571428569</v>
+        <v>35</v>
       </c>
       <c r="F75" s="12">
         <v>11</v>
@@ -2918,7 +2918,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="22">
+      <c r="A76" s="21">
         <v>27</v>
       </c>
       <c r="B76" s="6" t="s">
@@ -2931,7 +2931,7 @@
         <v>1460</v>
       </c>
       <c r="E76" s="7">
-        <v>36.571428571428569</v>
+        <v>37</v>
       </c>
       <c r="F76" s="12">
         <v>11</v>
@@ -2947,7 +2947,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="22">
+      <c r="A77" s="21">
         <v>27</v>
       </c>
       <c r="B77" s="6" t="s">
@@ -2960,7 +2960,7 @@
         <v>1460</v>
       </c>
       <c r="E77" s="7">
-        <v>39.857142857142861</v>
+        <v>40</v>
       </c>
       <c r="F77" s="12">
         <v>11</v>
@@ -2976,7 +2976,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="22">
+      <c r="A78" s="21">
         <v>28</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -2989,7 +2989,7 @@
         <v>1760</v>
       </c>
       <c r="E78" s="7">
-        <v>33.142857142857146</v>
+        <v>33</v>
       </c>
       <c r="F78" s="6">
         <v>0</v>
@@ -3005,7 +3005,7 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="22">
+      <c r="A79" s="21">
         <v>28</v>
       </c>
       <c r="B79" s="6" t="s">
@@ -3018,7 +3018,7 @@
         <v>1760</v>
       </c>
       <c r="E79" s="7">
-        <v>38.428571428571431</v>
+        <v>38</v>
       </c>
       <c r="F79" s="6">
         <v>0</v>
@@ -3034,7 +3034,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="22">
+      <c r="A80" s="21">
         <v>28</v>
       </c>
       <c r="B80" s="6" t="s">
@@ -3047,7 +3047,7 @@
         <v>1760</v>
       </c>
       <c r="E80" s="7">
-        <v>41.428571428571431</v>
+        <v>41</v>
       </c>
       <c r="F80" s="6">
         <v>0</v>
@@ -3063,7 +3063,7 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="22">
+      <c r="A81" s="21">
         <v>29</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -3076,7 +3076,7 @@
         <v>3600</v>
       </c>
       <c r="E81" s="7">
-        <v>39.857142857142854</v>
+        <v>40</v>
       </c>
       <c r="F81" s="6">
         <v>0</v>
@@ -3092,7 +3092,7 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="22">
+      <c r="A82" s="21">
         <v>30</v>
       </c>
       <c r="B82" s="6" t="s">
@@ -3105,7 +3105,7 @@
         <v>1290</v>
       </c>
       <c r="E82" s="7">
-        <v>41.428571428571431</v>
+        <v>41</v>
       </c>
       <c r="F82" s="6">
         <v>9</v>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="22">
+      <c r="A83" s="21">
         <v>31</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -3134,7 +3134,7 @@
         <v>910</v>
       </c>
       <c r="E83" s="7">
-        <v>32.142857142857146</v>
+        <v>32</v>
       </c>
       <c r="F83" s="6">
         <v>2</v>
@@ -3150,7 +3150,7 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="22">
+      <c r="A84" s="21">
         <v>31</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -3163,7 +3163,7 @@
         <v>910</v>
       </c>
       <c r="E84" s="7">
-        <v>33.142857142857139</v>
+        <v>33</v>
       </c>
       <c r="F84" s="6">
         <v>3</v>
@@ -3179,7 +3179,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="22">
+      <c r="A85" s="21">
         <v>31</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -3192,7 +3192,7 @@
         <v>910</v>
       </c>
       <c r="E85" s="7">
-        <v>34.142857142857139</v>
+        <v>34</v>
       </c>
       <c r="F85" s="6">
         <v>3</v>
@@ -3208,7 +3208,7 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="22">
+      <c r="A86" s="21">
         <v>31</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -3221,7 +3221,7 @@
         <v>910</v>
       </c>
       <c r="E86" s="7">
-        <v>35.142857142857139</v>
+        <v>35</v>
       </c>
       <c r="F86" s="6">
         <v>3</v>
@@ -3237,7 +3237,7 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="22">
+      <c r="A87" s="21">
         <v>31</v>
       </c>
       <c r="B87" s="6" t="s">
@@ -3250,7 +3250,7 @@
         <v>910</v>
       </c>
       <c r="E87" s="7">
-        <v>36.142857142857139</v>
+        <v>36</v>
       </c>
       <c r="F87" s="6">
         <v>3</v>
@@ -3258,7 +3258,7 @@
       <c r="G87" s="6">
         <v>0</v>
       </c>
-      <c r="H87" s="16">
+      <c r="H87" s="8">
         <v>1</v>
       </c>
       <c r="I87" s="8">
@@ -3266,7 +3266,7 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="22">
+      <c r="A88" s="21">
         <v>31</v>
       </c>
       <c r="B88" s="6" t="s">
@@ -3279,7 +3279,7 @@
         <v>910</v>
       </c>
       <c r="E88" s="7">
-        <v>37.428571428571431</v>
+        <v>37</v>
       </c>
       <c r="F88" s="6">
         <v>3</v>
@@ -3287,7 +3287,7 @@
       <c r="G88" s="6">
         <v>0</v>
       </c>
-      <c r="H88" s="16">
+      <c r="H88" s="8">
         <v>1</v>
       </c>
       <c r="I88" s="8">
@@ -3295,7 +3295,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="22">
+      <c r="A89" s="21">
         <v>31</v>
       </c>
       <c r="B89" s="6" t="s">
@@ -3308,7 +3308,7 @@
         <v>910</v>
       </c>
       <c r="E89" s="7">
-        <v>38.142857142857139</v>
+        <v>38</v>
       </c>
       <c r="F89" s="6">
         <v>3</v>
@@ -3316,7 +3316,7 @@
       <c r="G89" s="6">
         <v>0</v>
       </c>
-      <c r="H89" s="16">
+      <c r="H89" s="8">
         <v>1</v>
       </c>
       <c r="I89" s="8">
@@ -3324,7 +3324,7 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="22">
+      <c r="A90" s="21">
         <v>31</v>
       </c>
       <c r="B90" s="6" t="s">
@@ -3337,7 +3337,7 @@
         <v>910</v>
       </c>
       <c r="E90" s="7">
-        <v>40.142857142857139</v>
+        <v>40</v>
       </c>
       <c r="F90" s="6">
         <v>2</v>
@@ -3353,7 +3353,7 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="22">
+      <c r="A91" s="21">
         <v>31</v>
       </c>
       <c r="B91" s="6" t="s">
@@ -3366,7 +3366,7 @@
         <v>910</v>
       </c>
       <c r="E91" s="7">
-        <v>43.428571428571431</v>
+        <v>43</v>
       </c>
       <c r="F91" s="6">
         <v>9</v>
@@ -3382,7 +3382,7 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="22">
+      <c r="A92" s="21">
         <v>32</v>
       </c>
       <c r="B92" s="6" t="s">
@@ -3395,7 +3395,7 @@
         <v>3060</v>
       </c>
       <c r="E92" s="7">
-        <v>41.285714285714285</v>
+        <v>41</v>
       </c>
       <c r="F92" s="6">
         <v>0</v>
@@ -3411,7 +3411,7 @@
       </c>
     </row>
     <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="22">
+      <c r="A93" s="21">
         <v>33</v>
       </c>
       <c r="B93" s="6" t="s">
@@ -3424,7 +3424,7 @@
         <v>1250</v>
       </c>
       <c r="E93" s="7">
-        <v>31.428571428571427</v>
+        <v>31</v>
       </c>
       <c r="F93" s="6">
         <v>0</v>
@@ -3440,7 +3440,7 @@
       </c>
     </row>
     <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="22">
+      <c r="A94" s="21">
         <v>33</v>
       </c>
       <c r="B94" s="6" t="s">
@@ -3453,7 +3453,7 @@
         <v>1250</v>
       </c>
       <c r="E94" s="7">
-        <v>33.285714285714285</v>
+        <v>33</v>
       </c>
       <c r="F94" s="6">
         <v>0</v>
@@ -3469,7 +3469,7 @@
       </c>
     </row>
     <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="22">
+      <c r="A95" s="21">
         <v>33</v>
       </c>
       <c r="B95" s="6" t="s">
@@ -3482,7 +3482,7 @@
         <v>1250</v>
       </c>
       <c r="E95" s="7">
-        <v>35.714285714285715</v>
+        <v>36</v>
       </c>
       <c r="F95" s="6">
         <v>0</v>
@@ -3498,7 +3498,7 @@
       </c>
     </row>
     <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="22">
+      <c r="A96" s="21">
         <v>33</v>
       </c>
       <c r="B96" s="6" t="s">
@@ -3511,7 +3511,7 @@
         <v>1250</v>
       </c>
       <c r="E96" s="7">
-        <v>40.714285714285715</v>
+        <v>41</v>
       </c>
       <c r="F96" s="6">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="22">
+      <c r="A97" s="21">
         <v>34</v>
       </c>
       <c r="B97" s="6" t="s">
@@ -3540,7 +3540,7 @@
         <v>1460</v>
       </c>
       <c r="E97" s="7">
-        <v>37.571428571428569</v>
+        <v>38</v>
       </c>
       <c r="F97" s="6">
         <v>0</v>
@@ -3556,7 +3556,7 @@
       </c>
     </row>
     <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="22">
+      <c r="A98" s="21">
         <v>35</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -3569,7 +3569,7 @@
         <v>2380</v>
       </c>
       <c r="E98" s="7">
-        <v>38.571428571428569</v>
+        <v>39</v>
       </c>
       <c r="F98" s="6">
         <v>0</v>
@@ -3585,7 +3585,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="22">
+      <c r="A99" s="21">
         <v>36</v>
       </c>
       <c r="B99" s="6" t="s">
@@ -3614,7 +3614,7 @@
       </c>
     </row>
     <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="22">
+      <c r="A100" s="21">
         <v>36</v>
       </c>
       <c r="B100" s="6" t="s">
@@ -3627,7 +3627,7 @@
         <v>960</v>
       </c>
       <c r="E100" s="7">
-        <v>33.714285714285715</v>
+        <v>34</v>
       </c>
       <c r="F100" s="6">
         <v>0</v>
@@ -3643,7 +3643,7 @@
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="22">
+      <c r="A101" s="21">
         <v>37</v>
       </c>
       <c r="B101" s="6" t="s">
@@ -3672,7 +3672,7 @@
       </c>
     </row>
     <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="22">
+      <c r="A102" s="21">
         <v>38</v>
       </c>
       <c r="B102" s="6" t="s">
@@ -3685,7 +3685,7 @@
         <v>1970</v>
       </c>
       <c r="E102" s="7">
-        <v>39.571428571428569</v>
+        <v>40</v>
       </c>
       <c r="F102" s="6">
         <v>0</v>
@@ -3701,7 +3701,7 @@
       </c>
     </row>
     <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="22">
+      <c r="A103" s="21">
         <v>39</v>
       </c>
       <c r="B103" s="6" t="s">
@@ -3714,7 +3714,7 @@
         <v>540</v>
       </c>
       <c r="E103" s="7">
-        <v>39.571428571428569</v>
+        <v>40</v>
       </c>
       <c r="F103" s="6">
         <v>0</v>
@@ -3730,7 +3730,7 @@
       </c>
     </row>
     <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="22">
+      <c r="A104" s="21">
         <v>40</v>
       </c>
       <c r="B104" s="6" t="s">
@@ -3743,7 +3743,7 @@
         <v>1770</v>
       </c>
       <c r="E104" s="7">
-        <v>35.571428571428569</v>
+        <v>36</v>
       </c>
       <c r="F104" s="6">
         <v>12</v>
@@ -3759,7 +3759,7 @@
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="22">
+      <c r="A105" s="21">
         <v>40</v>
       </c>
       <c r="B105" s="6" t="s">
@@ -3788,7 +3788,7 @@
       </c>
     </row>
     <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="22">
+      <c r="A106" s="21">
         <v>40</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -3817,7 +3817,7 @@
       </c>
     </row>
     <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="22">
+      <c r="A107" s="21">
         <v>40</v>
       </c>
       <c r="B107" s="6" t="s">
@@ -3846,7 +3846,7 @@
       </c>
     </row>
     <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="22">
+      <c r="A108" s="21">
         <v>41</v>
       </c>
       <c r="B108" s="6" t="s">
@@ -3859,7 +3859,7 @@
         <v>1770</v>
       </c>
       <c r="E108" s="7">
-        <v>35.571428571428569</v>
+        <v>36</v>
       </c>
       <c r="F108" s="6">
         <v>0</v>
@@ -3875,7 +3875,7 @@
       </c>
     </row>
     <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="22">
+      <c r="A109" s="21">
         <v>41</v>
       </c>
       <c r="B109" s="6" t="s">
@@ -3904,7 +3904,7 @@
       </c>
     </row>
     <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="22">
+      <c r="A110" s="21">
         <v>41</v>
       </c>
       <c r="B110" s="6" t="s">
@@ -3933,7 +3933,7 @@
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="22">
+      <c r="A111" s="21">
         <v>41</v>
       </c>
       <c r="B111" s="6" t="s">
@@ -3962,7 +3962,7 @@
       </c>
     </row>
     <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="22">
+      <c r="A112" s="21">
         <v>42</v>
       </c>
       <c r="B112" s="6" t="s">
@@ -3975,7 +3975,7 @@
         <v>2700</v>
       </c>
       <c r="E112" s="7">
-        <v>41.285714285714285</v>
+        <v>41</v>
       </c>
       <c r="F112" s="12">
         <v>11</v>
@@ -3991,7 +3991,7 @@
       </c>
     </row>
     <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="22">
+      <c r="A113" s="21">
         <v>43</v>
       </c>
       <c r="B113" s="6" t="s">
@@ -4004,7 +4004,7 @@
         <v>550</v>
       </c>
       <c r="E113" s="7">
-        <v>32.428571428571431</v>
+        <v>32</v>
       </c>
       <c r="F113" s="6">
         <v>8</v>
@@ -4020,7 +4020,7 @@
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="22">
+      <c r="A114" s="21">
         <v>43</v>
       </c>
       <c r="B114" s="6" t="s">
@@ -4033,7 +4033,7 @@
         <v>550</v>
       </c>
       <c r="E114" s="7">
-        <v>32.857142857142861</v>
+        <v>33</v>
       </c>
       <c r="F114" s="6">
         <v>8</v>
@@ -4049,7 +4049,7 @@
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="22">
+      <c r="A115" s="21">
         <v>43</v>
       </c>
       <c r="B115" s="6" t="s">
@@ -4062,7 +4062,7 @@
         <v>550</v>
       </c>
       <c r="E115" s="7">
-        <v>33.428571428571431</v>
+        <v>33</v>
       </c>
       <c r="F115" s="6">
         <v>8</v>
@@ -4078,7 +4078,7 @@
       </c>
     </row>
     <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="22">
+      <c r="A116" s="21">
         <v>43</v>
       </c>
       <c r="B116" s="6" t="s">
@@ -4091,7 +4091,7 @@
         <v>550</v>
       </c>
       <c r="E116" s="7">
-        <v>34.857142857142861</v>
+        <v>35</v>
       </c>
       <c r="F116" s="6">
         <v>8</v>
@@ -4107,7 +4107,7 @@
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="22">
+      <c r="A117" s="21">
         <v>43</v>
       </c>
       <c r="B117" s="6" t="s">
@@ -4120,7 +4120,7 @@
         <v>550</v>
       </c>
       <c r="E117" s="7">
-        <v>35.714285714285715</v>
+        <v>36</v>
       </c>
       <c r="F117" s="6">
         <v>8</v>
@@ -4136,7 +4136,7 @@
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="22">
+      <c r="A118" s="21">
         <v>43</v>
       </c>
       <c r="B118" s="6" t="s">
@@ -4149,7 +4149,7 @@
         <v>550</v>
       </c>
       <c r="E118" s="7">
-        <v>36.428571428571431</v>
+        <v>36</v>
       </c>
       <c r="F118" s="6">
         <v>8</v>
@@ -4165,7 +4165,7 @@
       </c>
     </row>
     <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="22">
+      <c r="A119" s="21">
         <v>43</v>
       </c>
       <c r="B119" s="6" t="s">
@@ -4178,7 +4178,7 @@
         <v>550</v>
       </c>
       <c r="E119" s="7">
-        <v>38.714285714285715</v>
+        <v>39</v>
       </c>
       <c r="F119" s="6">
         <v>8</v>
@@ -4194,7 +4194,7 @@
       </c>
     </row>
     <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="22">
+      <c r="A120" s="21">
         <v>43</v>
       </c>
       <c r="B120" s="6" t="s">
@@ -4207,7 +4207,7 @@
         <v>550</v>
       </c>
       <c r="E120" s="7">
-        <v>38.857142857142861</v>
+        <v>39</v>
       </c>
       <c r="F120" s="6">
         <v>8</v>
@@ -4223,7 +4223,7 @@
       </c>
     </row>
     <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="22">
+      <c r="A121" s="21">
         <v>43</v>
       </c>
       <c r="B121" s="6" t="s">
@@ -4236,7 +4236,7 @@
         <v>550</v>
       </c>
       <c r="E121" s="7">
-        <v>39.714285714285715</v>
+        <v>40</v>
       </c>
       <c r="F121" s="6">
         <v>8</v>
@@ -4252,7 +4252,7 @@
       </c>
     </row>
     <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="22">
+      <c r="A122" s="21">
         <v>43</v>
       </c>
       <c r="B122" s="6" t="s">
@@ -4265,7 +4265,7 @@
         <v>550</v>
       </c>
       <c r="E122" s="7">
-        <v>40.714285714285715</v>
+        <v>41</v>
       </c>
       <c r="F122" s="6">
         <v>8</v>
@@ -4281,7 +4281,7 @@
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="22">
+      <c r="A123" s="21">
         <v>43</v>
       </c>
       <c r="B123" s="6" t="s">
@@ -4294,7 +4294,7 @@
         <v>550</v>
       </c>
       <c r="E123" s="7">
-        <v>42.714285714285715</v>
+        <v>43</v>
       </c>
       <c r="F123" s="6">
         <v>8</v>
@@ -4310,7 +4310,7 @@
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="22">
+      <c r="A124" s="21">
         <v>43</v>
       </c>
       <c r="B124" s="6" t="s">
@@ -4323,7 +4323,7 @@
         <v>550</v>
       </c>
       <c r="E124" s="7">
-        <v>46.714285714285715</v>
+        <v>47</v>
       </c>
       <c r="F124" s="6">
         <v>8</v>
@@ -4339,7 +4339,7 @@
       </c>
     </row>
     <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="22">
+      <c r="A125" s="21">
         <v>43</v>
       </c>
       <c r="B125" s="6" t="s">
@@ -4352,7 +4352,7 @@
         <v>550</v>
       </c>
       <c r="E125" s="7">
-        <v>47.285714285714285</v>
+        <v>47</v>
       </c>
       <c r="F125" s="6">
         <v>8</v>
@@ -4368,7 +4368,7 @@
       </c>
     </row>
     <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="22">
+      <c r="A126" s="21">
         <v>43</v>
       </c>
       <c r="B126" s="6" t="s">
@@ -4381,7 +4381,7 @@
         <v>550</v>
       </c>
       <c r="E126" s="7">
-        <v>48.285714285714285</v>
+        <v>48</v>
       </c>
       <c r="F126" s="6">
         <v>8</v>
@@ -4397,7 +4397,7 @@
       </c>
     </row>
     <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="22">
+      <c r="A127" s="21">
         <v>43</v>
       </c>
       <c r="B127" s="6" t="s">
@@ -4410,7 +4410,7 @@
         <v>550</v>
       </c>
       <c r="E127" s="7">
-        <v>49.714285714285715</v>
+        <v>50</v>
       </c>
       <c r="F127" s="6">
         <v>8</v>
@@ -4426,7 +4426,7 @@
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="22">
+      <c r="A128" s="21">
         <v>43</v>
       </c>
       <c r="B128" s="6" t="s">
@@ -4439,7 +4439,7 @@
         <v>550</v>
       </c>
       <c r="E128" s="7">
-        <v>56.571428571428569</v>
+        <v>57</v>
       </c>
       <c r="F128" s="6">
         <v>8</v>
@@ -4455,7 +4455,7 @@
       </c>
     </row>
     <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="22">
+      <c r="A129" s="21">
         <v>44</v>
       </c>
       <c r="B129" s="6" t="s">
@@ -4468,7 +4468,7 @@
         <v>1370</v>
       </c>
       <c r="E129" s="7">
-        <v>33.571428571428569</v>
+        <v>34</v>
       </c>
       <c r="F129" s="6">
         <v>0</v>
@@ -4484,7 +4484,7 @@
       </c>
     </row>
     <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="22">
+      <c r="A130" s="21">
         <v>44</v>
       </c>
       <c r="B130" s="6" t="s">
@@ -4497,7 +4497,7 @@
         <v>1370</v>
       </c>
       <c r="E130" s="7">
-        <v>35.428571428571431</v>
+        <v>35</v>
       </c>
       <c r="F130" s="6">
         <v>0</v>
@@ -4513,7 +4513,7 @@
       </c>
     </row>
     <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="22">
+      <c r="A131" s="21">
         <v>44</v>
       </c>
       <c r="B131" s="6" t="s">
@@ -4526,7 +4526,7 @@
         <v>1370</v>
       </c>
       <c r="E131" s="7">
-        <v>41.857142857142861</v>
+        <v>42</v>
       </c>
       <c r="F131" s="6">
         <v>0</v>
@@ -4542,7 +4542,7 @@
       </c>
     </row>
     <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="22">
+      <c r="A132" s="21">
         <v>45</v>
       </c>
       <c r="B132" s="6" t="s">
@@ -4555,7 +4555,7 @@
         <v>1120</v>
       </c>
       <c r="E132" s="7">
-        <v>37.857142857142861</v>
+        <v>38</v>
       </c>
       <c r="F132" s="6">
         <v>2</v>
@@ -4571,7 +4571,7 @@
       </c>
     </row>
     <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="22">
+      <c r="A133" s="21">
         <v>45</v>
       </c>
       <c r="B133" s="6" t="s">
@@ -4584,7 +4584,7 @@
         <v>1120</v>
       </c>
       <c r="E133" s="7">
-        <v>42.285714285714285</v>
+        <v>42</v>
       </c>
       <c r="F133" s="6">
         <v>9</v>
@@ -4600,7 +4600,7 @@
       </c>
     </row>
     <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="22">
+      <c r="A134" s="21">
         <v>46</v>
       </c>
       <c r="B134" s="6" t="s">
@@ -4613,7 +4613,7 @@
         <v>2765</v>
       </c>
       <c r="E134" s="7">
-        <v>37.285714285714285</v>
+        <v>37</v>
       </c>
       <c r="F134" s="6">
         <v>0</v>
@@ -4629,7 +4629,7 @@
       </c>
     </row>
     <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="22">
+      <c r="A135" s="21">
         <v>47</v>
       </c>
       <c r="B135" s="6" t="s">
@@ -4642,7 +4642,7 @@
         <v>1730</v>
       </c>
       <c r="E135" s="7">
-        <v>33.142857142857146</v>
+        <v>33</v>
       </c>
       <c r="F135" s="6">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
     </row>
     <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="22">
+      <c r="A136" s="21">
         <v>47</v>
       </c>
       <c r="B136" s="6" t="s">
@@ -4671,7 +4671,7 @@
         <v>1730</v>
       </c>
       <c r="E136" s="7">
-        <v>38.428571428571431</v>
+        <v>38</v>
       </c>
       <c r="F136" s="6">
         <v>0</v>
@@ -4687,7 +4687,7 @@
       </c>
     </row>
     <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="22">
+      <c r="A137" s="21">
         <v>47</v>
       </c>
       <c r="B137" s="6" t="s">
@@ -4700,7 +4700,7 @@
         <v>1730</v>
       </c>
       <c r="E137" s="7">
-        <v>40.285714285714285</v>
+        <v>40</v>
       </c>
       <c r="F137" s="6">
         <v>0</v>
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="22">
+      <c r="A138" s="21">
         <v>48</v>
       </c>
       <c r="B138" s="6" t="s">
@@ -4729,7 +4729,7 @@
         <v>1680</v>
       </c>
       <c r="E138" s="7">
-        <v>33.142857142857146</v>
+        <v>33</v>
       </c>
       <c r="F138" s="6">
         <v>0</v>
@@ -4745,7 +4745,7 @@
       </c>
     </row>
     <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="22">
+      <c r="A139" s="21">
         <v>48</v>
       </c>
       <c r="B139" s="6" t="s">
@@ -4758,7 +4758,7 @@
         <v>1680</v>
       </c>
       <c r="E139" s="7">
-        <v>38.428571428571431</v>
+        <v>38</v>
       </c>
       <c r="F139" s="6">
         <v>0</v>
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="22">
+      <c r="A140" s="21">
         <v>48</v>
       </c>
       <c r="B140" s="6" t="s">
@@ -4787,7 +4787,7 @@
         <v>1680</v>
       </c>
       <c r="E140" s="7">
-        <v>40.285714285714285</v>
+        <v>40</v>
       </c>
       <c r="F140" s="6">
         <v>0</v>
@@ -4803,7 +4803,7 @@
       </c>
     </row>
     <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="22">
+      <c r="A141" s="21">
         <v>49</v>
       </c>
       <c r="B141" s="6" t="s">
@@ -4816,7 +4816,7 @@
         <v>1220</v>
       </c>
       <c r="E141" s="7">
-        <v>32.142857142857146</v>
+        <v>32</v>
       </c>
       <c r="F141" s="6">
         <v>0</v>
@@ -4832,7 +4832,7 @@
       </c>
     </row>
     <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="22">
+      <c r="A142" s="21">
         <v>49</v>
       </c>
       <c r="B142" s="6" t="s">
@@ -4845,7 +4845,7 @@
         <v>1220</v>
       </c>
       <c r="E142" s="7">
-        <v>34.142857142857146</v>
+        <v>34</v>
       </c>
       <c r="F142" s="6">
         <v>0</v>
@@ -4861,7 +4861,7 @@
       </c>
     </row>
     <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="22">
+      <c r="A143" s="21">
         <v>49</v>
       </c>
       <c r="B143" s="6" t="s">
@@ -4874,7 +4874,7 @@
         <v>1220</v>
       </c>
       <c r="E143" s="7">
-        <v>36.142857142857146</v>
+        <v>36</v>
       </c>
       <c r="F143" s="6">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
     </row>
     <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="22">
+      <c r="A144" s="21">
         <v>50</v>
       </c>
       <c r="B144" s="6" t="s">
@@ -4903,7 +4903,7 @@
         <v>1790</v>
       </c>
       <c r="E144" s="7">
-        <v>33.428571428571431</v>
+        <v>33</v>
       </c>
       <c r="F144" s="6">
         <v>0</v>
@@ -4919,7 +4919,7 @@
       </c>
     </row>
     <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="22">
+      <c r="A145" s="21">
         <v>50</v>
       </c>
       <c r="B145" s="6" t="s">
@@ -4932,7 +4932,7 @@
         <v>1790</v>
       </c>
       <c r="E145" s="7">
-        <v>37.857142857142854</v>
+        <v>38</v>
       </c>
       <c r="F145" s="6">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
     </row>
     <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="22">
+      <c r="A146" s="21">
         <v>50</v>
       </c>
       <c r="B146" s="6" t="s">
@@ -4961,7 +4961,7 @@
         <v>1790</v>
       </c>
       <c r="E146" s="7">
-        <v>40.857142857142861</v>
+        <v>41</v>
       </c>
       <c r="F146" s="6">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
     </row>
     <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="22">
+      <c r="A147" s="21">
         <v>51</v>
       </c>
       <c r="B147" s="6" t="s">
@@ -4990,7 +4990,7 @@
         <v>600</v>
       </c>
       <c r="E147" s="7">
-        <v>35.428571428571431</v>
+        <v>35</v>
       </c>
       <c r="F147" s="6">
         <v>3</v>
@@ -5006,7 +5006,7 @@
       </c>
     </row>
     <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="22">
+      <c r="A148" s="21">
         <v>51</v>
       </c>
       <c r="B148" s="6" t="s">
@@ -5019,7 +5019,7 @@
         <v>600</v>
       </c>
       <c r="E148" s="7">
-        <v>36.428571428571431</v>
+        <v>36</v>
       </c>
       <c r="F148" s="6">
         <v>3</v>
@@ -5035,7 +5035,7 @@
       </c>
     </row>
     <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="22">
+      <c r="A149" s="21">
         <v>51</v>
       </c>
       <c r="B149" s="6" t="s">
@@ -5048,7 +5048,7 @@
         <v>600</v>
       </c>
       <c r="E149" s="7">
-        <v>41.714285714285715</v>
+        <v>42</v>
       </c>
       <c r="F149" s="6">
         <v>3</v>
@@ -5064,7 +5064,7 @@
       </c>
     </row>
     <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A150" s="22">
+      <c r="A150" s="21">
         <v>51</v>
       </c>
       <c r="B150" s="6" t="s">
@@ -5077,7 +5077,7 @@
         <v>600</v>
       </c>
       <c r="E150" s="7">
-        <v>45.714285714285715</v>
+        <v>46</v>
       </c>
       <c r="F150" s="6">
         <v>9</v>
@@ -5093,7 +5093,7 @@
       </c>
     </row>
     <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="22">
+      <c r="A151" s="21">
         <v>52</v>
       </c>
       <c r="B151" s="6" t="s">
@@ -5106,7 +5106,7 @@
         <v>820</v>
       </c>
       <c r="E151" s="7">
-        <v>31.142857142857142</v>
+        <v>31</v>
       </c>
       <c r="F151" s="6">
         <v>1</v>
@@ -5122,7 +5122,7 @@
       </c>
     </row>
     <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="22">
+      <c r="A152" s="21">
         <v>52</v>
       </c>
       <c r="B152" s="6" t="s">
@@ -5135,7 +5135,7 @@
         <v>820</v>
       </c>
       <c r="E152" s="7">
-        <v>32.142857142857146</v>
+        <v>32</v>
       </c>
       <c r="F152" s="6">
         <v>2</v>
@@ -5151,7 +5151,7 @@
       </c>
     </row>
     <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="22">
+      <c r="A153" s="21">
         <v>52</v>
       </c>
       <c r="B153" s="6" t="s">
@@ -5164,7 +5164,7 @@
         <v>820</v>
       </c>
       <c r="E153" s="7">
-        <v>33.142857142857146</v>
+        <v>33</v>
       </c>
       <c r="F153" s="6">
         <v>3</v>
@@ -5180,7 +5180,7 @@
       </c>
     </row>
     <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="22">
+      <c r="A154" s="21">
         <v>52</v>
       </c>
       <c r="B154" s="6" t="s">
@@ -5193,7 +5193,7 @@
         <v>820</v>
       </c>
       <c r="E154" s="7">
-        <v>34.142857142857139</v>
+        <v>34</v>
       </c>
       <c r="F154" s="6">
         <v>3</v>
@@ -5209,7 +5209,7 @@
       </c>
     </row>
     <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="22">
+      <c r="A155" s="21">
         <v>52</v>
       </c>
       <c r="B155" s="6" t="s">
@@ -5222,7 +5222,7 @@
         <v>820</v>
       </c>
       <c r="E155" s="7">
-        <v>36.142857142857139</v>
+        <v>36</v>
       </c>
       <c r="F155" s="6">
         <v>3</v>
@@ -5238,7 +5238,7 @@
       </c>
     </row>
     <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" s="22">
+      <c r="A156" s="21">
         <v>52</v>
       </c>
       <c r="B156" s="6" t="s">
@@ -5251,7 +5251,7 @@
         <v>820</v>
       </c>
       <c r="E156" s="7">
-        <v>42.285714285714285</v>
+        <v>42</v>
       </c>
       <c r="F156" s="6">
         <v>3</v>
@@ -5267,7 +5267,7 @@
       </c>
     </row>
     <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="22">
+      <c r="A157" s="21">
         <v>52</v>
       </c>
       <c r="B157" s="6" t="s">
@@ -5280,7 +5280,7 @@
         <v>820</v>
       </c>
       <c r="E157" s="7">
-        <v>46.428571428571431</v>
+        <v>46</v>
       </c>
       <c r="F157" s="6">
         <v>2</v>
@@ -5296,7 +5296,7 @@
       </c>
     </row>
     <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="22">
+      <c r="A158" s="21">
         <v>52</v>
       </c>
       <c r="B158" s="6" t="s">
@@ -5309,7 +5309,7 @@
         <v>820</v>
       </c>
       <c r="E158" s="7">
-        <v>75.428571428571431</v>
+        <v>75</v>
       </c>
       <c r="F158" s="6">
         <v>9</v>
@@ -5325,7 +5325,7 @@
       </c>
     </row>
     <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="22">
+      <c r="A159" s="21">
         <v>53</v>
       </c>
       <c r="B159" s="6" t="s">
@@ -5338,7 +5338,7 @@
         <v>2310</v>
       </c>
       <c r="E159" s="7">
-        <v>34.714285714285715</v>
+        <v>35</v>
       </c>
       <c r="F159" s="6">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="22">
+      <c r="A160" s="21">
         <v>54</v>
       </c>
       <c r="B160" s="6" t="s">
@@ -5367,7 +5367,7 @@
         <v>1410</v>
       </c>
       <c r="E160" s="7">
-        <v>37.285714285714285</v>
+        <v>37</v>
       </c>
       <c r="F160" s="6">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
     </row>
     <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="22">
+      <c r="A161" s="21">
         <v>54</v>
       </c>
       <c r="B161" s="6" t="s">
@@ -5396,7 +5396,7 @@
         <v>1410</v>
       </c>
       <c r="E161" s="7">
-        <v>42.571428571428569</v>
+        <v>43</v>
       </c>
       <c r="F161" s="6">
         <v>0</v>
@@ -5412,7 +5412,7 @@
       </c>
     </row>
     <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="23">
+      <c r="A162" s="22">
         <v>55</v>
       </c>
       <c r="B162" s="6" t="s">
@@ -5425,7 +5425,7 @@
         <v>3245</v>
       </c>
       <c r="E162" s="7">
-        <v>39.857142857142854</v>
+        <v>40</v>
       </c>
       <c r="F162" s="6">
         <v>13</v>
@@ -5441,7 +5441,7 @@
       </c>
     </row>
     <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" s="23">
+      <c r="A163" s="22">
         <v>55</v>
       </c>
       <c r="B163" s="6" t="s">
@@ -5454,7 +5454,7 @@
         <v>3245</v>
       </c>
       <c r="E163" s="7">
-        <v>40.857142857142854</v>
+        <v>41</v>
       </c>
       <c r="F163" s="6">
         <v>13</v>
@@ -5470,7 +5470,7 @@
       </c>
     </row>
     <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="23">
+      <c r="A164" s="22">
         <v>55</v>
       </c>
       <c r="B164" s="6" t="s">
@@ -5483,7 +5483,7 @@
         <v>3245</v>
       </c>
       <c r="E164" s="7">
-        <v>41.857142857142854</v>
+        <v>42</v>
       </c>
       <c r="F164" s="6">
         <v>13</v>
@@ -5499,7 +5499,7 @@
       </c>
     </row>
     <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="23">
+      <c r="A165" s="22">
         <v>55</v>
       </c>
       <c r="B165" s="6" t="s">
@@ -5512,7 +5512,7 @@
         <v>3245</v>
       </c>
       <c r="E165" s="7">
-        <v>42.857142857142854</v>
+        <v>43</v>
       </c>
       <c r="F165" s="6">
         <v>13</v>
@@ -5528,7 +5528,7 @@
       </c>
     </row>
     <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="23">
+      <c r="A166" s="22">
         <v>55</v>
       </c>
       <c r="B166" s="6" t="s">
@@ -5541,7 +5541,7 @@
         <v>3245</v>
       </c>
       <c r="E166" s="7">
-        <v>43.857142857142854</v>
+        <v>44</v>
       </c>
       <c r="F166" s="6">
         <v>13</v>
@@ -5557,7 +5557,7 @@
       </c>
     </row>
     <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="23">
+      <c r="A167" s="22">
         <v>55</v>
       </c>
       <c r="B167" s="6" t="s">
@@ -5570,7 +5570,7 @@
         <v>3245</v>
       </c>
       <c r="E167" s="7">
-        <v>44.714285714285715</v>
+        <v>45</v>
       </c>
       <c r="F167" s="6">
         <v>13</v>
@@ -5586,7 +5586,7 @@
       </c>
     </row>
     <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="23">
+      <c r="A168" s="22">
         <v>55</v>
       </c>
       <c r="B168" s="6" t="s">
@@ -5599,7 +5599,7 @@
         <v>3245</v>
       </c>
       <c r="E168" s="7">
-        <v>47.142857142857139</v>
+        <v>47</v>
       </c>
       <c r="F168" s="6">
         <v>13</v>
@@ -5615,7 +5615,7 @@
       </c>
     </row>
     <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="23">
+      <c r="A169" s="22">
         <v>55</v>
       </c>
       <c r="B169" s="6" t="s">
@@ -5628,7 +5628,7 @@
         <v>3245</v>
       </c>
       <c r="E169" s="7">
-        <v>53.142857142857139</v>
+        <v>53</v>
       </c>
       <c r="F169" s="6">
         <v>13</v>
@@ -5644,7 +5644,7 @@
       </c>
     </row>
     <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="23">
+      <c r="A170" s="22">
         <v>55</v>
       </c>
       <c r="B170" s="6" t="s">
@@ -5657,7 +5657,7 @@
         <v>3245</v>
       </c>
       <c r="E170" s="7">
-        <v>78.142857142857139</v>
+        <v>78</v>
       </c>
       <c r="F170" s="6">
         <v>13</v>
@@ -5673,7 +5673,7 @@
       </c>
     </row>
     <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A171" s="23">
+      <c r="A171" s="22">
         <v>56</v>
       </c>
       <c r="B171" s="6" t="s">
@@ -5686,7 +5686,7 @@
         <v>1180</v>
       </c>
       <c r="E171" s="7">
-        <v>35.428571428571431</v>
+        <v>35</v>
       </c>
       <c r="F171" s="6">
         <v>0</v>
@@ -5702,7 +5702,7 @@
       </c>
     </row>
     <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A172" s="23">
+      <c r="A172" s="22">
         <v>56</v>
       </c>
       <c r="B172" s="6" t="s">
@@ -5715,7 +5715,7 @@
         <v>1180</v>
       </c>
       <c r="E172" s="7">
-        <v>37.571428571428569</v>
+        <v>38</v>
       </c>
       <c r="F172" s="6">
         <v>0</v>
@@ -5731,7 +5731,7 @@
       </c>
     </row>
     <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A173" s="23">
+      <c r="A173" s="22">
         <v>56</v>
       </c>
       <c r="B173" s="6" t="s">
@@ -5744,7 +5744,7 @@
         <v>1180</v>
       </c>
       <c r="E173" s="7">
-        <v>41.857142857142861</v>
+        <v>42</v>
       </c>
       <c r="F173" s="6">
         <v>0</v>
@@ -5760,7 +5760,7 @@
       </c>
     </row>
     <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A174" s="23">
+      <c r="A174" s="22">
         <v>57</v>
       </c>
       <c r="B174" s="6" t="s">
@@ -5773,7 +5773,7 @@
         <v>1180</v>
       </c>
       <c r="E174" s="7">
-        <v>33.285714285714285</v>
+        <v>33</v>
       </c>
       <c r="F174" s="6">
         <v>0</v>
@@ -5789,7 +5789,7 @@
       </c>
     </row>
     <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="23">
+      <c r="A175" s="22">
         <v>57</v>
       </c>
       <c r="B175" s="6" t="s">
@@ -5802,7 +5802,7 @@
         <v>1180</v>
       </c>
       <c r="E175" s="7">
-        <v>37.285714285714285</v>
+        <v>37</v>
       </c>
       <c r="F175" s="6">
         <v>0</v>
@@ -5818,7 +5818,7 @@
       </c>
     </row>
     <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="23">
+      <c r="A176" s="22">
         <v>57</v>
       </c>
       <c r="B176" s="6" t="s">
@@ -5831,7 +5831,7 @@
         <v>1180</v>
       </c>
       <c r="E176" s="7">
-        <v>39.285714285714285</v>
+        <v>39</v>
       </c>
       <c r="F176" s="6">
         <v>0</v>
@@ -5847,7 +5847,7 @@
       </c>
     </row>
     <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="23">
+      <c r="A177" s="22">
         <v>58</v>
       </c>
       <c r="B177" s="6" t="s">
@@ -5860,7 +5860,7 @@
         <v>1490</v>
       </c>
       <c r="E177" s="7">
-        <v>33.142857142857146</v>
+        <v>33</v>
       </c>
       <c r="F177" s="6">
         <v>0</v>
@@ -5876,7 +5876,7 @@
       </c>
     </row>
     <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A178" s="23">
+      <c r="A178" s="22">
         <v>58</v>
       </c>
       <c r="B178" s="6" t="s">
@@ -5889,7 +5889,7 @@
         <v>1490</v>
       </c>
       <c r="E178" s="7">
-        <v>35.142857142857146</v>
+        <v>35</v>
       </c>
       <c r="F178" s="6">
         <v>0</v>
@@ -5905,7 +5905,7 @@
       </c>
     </row>
     <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" s="23">
+      <c r="A179" s="22">
         <v>58</v>
       </c>
       <c r="B179" s="6" t="s">
@@ -5918,7 +5918,7 @@
         <v>1490</v>
       </c>
       <c r="E179" s="7">
-        <v>38.428571428571431</v>
+        <v>38</v>
       </c>
       <c r="F179" s="6">
         <v>0</v>
@@ -5934,7 +5934,7 @@
       </c>
     </row>
     <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A180" s="23">
+      <c r="A180" s="22">
         <v>59</v>
       </c>
       <c r="B180" s="6" t="s">
@@ -5963,7 +5963,7 @@
       </c>
     </row>
     <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A181" s="23">
+      <c r="A181" s="22">
         <v>59</v>
       </c>
       <c r="B181" s="6" t="s">
@@ -5992,7 +5992,7 @@
       </c>
     </row>
     <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" s="23">
+      <c r="A182" s="22">
         <v>59</v>
       </c>
       <c r="B182" s="6" t="s">
@@ -6021,7 +6021,7 @@
       </c>
     </row>
     <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" s="23">
+      <c r="A183" s="22">
         <v>60</v>
       </c>
       <c r="B183" s="6" t="s">
@@ -6034,7 +6034,7 @@
         <v>3840</v>
       </c>
       <c r="E183" s="7">
-        <v>40.714285714285715</v>
+        <v>41</v>
       </c>
       <c r="F183" s="6">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
     </row>
     <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="23">
+      <c r="A184" s="22">
         <v>61</v>
       </c>
       <c r="B184" s="6" t="s">
@@ -6079,7 +6079,7 @@
       </c>
     </row>
     <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A185" s="23">
+      <c r="A185" s="22">
         <v>61</v>
       </c>
       <c r="B185" s="6" t="s">
@@ -6108,7 +6108,7 @@
       </c>
     </row>
     <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A186" s="23">
+      <c r="A186" s="22">
         <v>61</v>
       </c>
       <c r="B186" s="6" t="s">
@@ -6121,7 +6121,7 @@
         <v>880</v>
       </c>
       <c r="E186" s="7">
-        <v>42.285714285714285</v>
+        <v>42</v>
       </c>
       <c r="F186" s="6">
         <v>0</v>
@@ -6137,7 +6137,7 @@
       </c>
     </row>
     <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A187" s="23">
+      <c r="A187" s="22">
         <v>62</v>
       </c>
       <c r="B187" s="6" t="s">
@@ -6150,7 +6150,7 @@
         <v>900</v>
       </c>
       <c r="E187" s="7">
-        <v>34.857142857142854</v>
+        <v>35</v>
       </c>
       <c r="F187" s="6">
         <v>0</v>
@@ -6166,7 +6166,7 @@
       </c>
     </row>
     <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A188" s="23">
+      <c r="A188" s="22">
         <v>62</v>
       </c>
       <c r="B188" s="6" t="s">
@@ -6179,7 +6179,7 @@
         <v>900</v>
       </c>
       <c r="E188" s="7">
-        <v>39.142857142857139</v>
+        <v>39</v>
       </c>
       <c r="F188" s="6">
         <v>0</v>
@@ -6195,7 +6195,7 @@
       </c>
     </row>
     <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A189" s="23">
+      <c r="A189" s="22">
         <v>63</v>
       </c>
       <c r="B189" s="6" t="s">
@@ -6208,7 +6208,7 @@
         <v>3000</v>
       </c>
       <c r="E189" s="7">
-        <v>35.714285714285715</v>
+        <v>36</v>
       </c>
       <c r="F189" s="6">
         <v>0</v>
@@ -6224,7 +6224,7 @@
       </c>
     </row>
     <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="23">
+      <c r="A190" s="22">
         <v>63</v>
       </c>
       <c r="B190" s="6" t="s">
@@ -6253,7 +6253,7 @@
       </c>
     </row>
     <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="23">
+      <c r="A191" s="22">
         <v>64</v>
       </c>
       <c r="B191" s="6" t="s">
@@ -6266,7 +6266,7 @@
         <v>990</v>
       </c>
       <c r="E191" s="7">
-        <v>32.857142857142854</v>
+        <v>33</v>
       </c>
       <c r="F191" s="6">
         <v>0</v>
@@ -6282,7 +6282,7 @@
       </c>
     </row>
     <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A192" s="23">
+      <c r="A192" s="22">
         <v>64</v>
       </c>
       <c r="B192" s="6" t="s">
@@ -6295,7 +6295,7 @@
         <v>990</v>
       </c>
       <c r="E192" s="7">
-        <v>36.857142857142854</v>
+        <v>37</v>
       </c>
       <c r="F192" s="6">
         <v>0</v>
@@ -6311,7 +6311,7 @@
       </c>
     </row>
     <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A193" s="23">
+      <c r="A193" s="22">
         <v>64</v>
       </c>
       <c r="B193" s="6" t="s">
@@ -6324,7 +6324,7 @@
         <v>990</v>
       </c>
       <c r="E193" s="7">
-        <v>40.142857142857139</v>
+        <v>40</v>
       </c>
       <c r="F193" s="6">
         <v>0</v>
@@ -6340,7 +6340,7 @@
       </c>
     </row>
     <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A194" s="23">
+      <c r="A194" s="22">
         <v>65</v>
       </c>
       <c r="B194" s="6" t="s">
@@ -6353,7 +6353,7 @@
         <v>950</v>
       </c>
       <c r="E194" s="7">
-        <v>31.714285714285715</v>
+        <v>32</v>
       </c>
       <c r="F194" s="6">
         <v>0</v>
@@ -6369,7 +6369,7 @@
       </c>
     </row>
     <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A195" s="23">
+      <c r="A195" s="22">
         <v>65</v>
       </c>
       <c r="B195" s="6" t="s">
@@ -6382,7 +6382,7 @@
         <v>950</v>
       </c>
       <c r="E195" s="7">
-        <v>33.714285714285715</v>
+        <v>34</v>
       </c>
       <c r="F195" s="6">
         <v>0</v>
@@ -6398,7 +6398,7 @@
       </c>
     </row>
     <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A196" s="23">
+      <c r="A196" s="22">
         <v>65</v>
       </c>
       <c r="B196" s="6" t="s">
@@ -6411,7 +6411,7 @@
         <v>950</v>
       </c>
       <c r="E196" s="7">
-        <v>35.571428571428569</v>
+        <v>36</v>
       </c>
       <c r="F196" s="6">
         <v>0</v>
@@ -6427,7 +6427,7 @@
       </c>
     </row>
     <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A197" s="23">
+      <c r="A197" s="22">
         <v>66</v>
       </c>
       <c r="B197" s="6" t="s">
@@ -6440,7 +6440,7 @@
         <v>810</v>
       </c>
       <c r="E197" s="7">
-        <v>31.285714285714285</v>
+        <v>31</v>
       </c>
       <c r="F197" s="6">
         <v>1</v>
@@ -6456,7 +6456,7 @@
       </c>
     </row>
     <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A198" s="23">
+      <c r="A198" s="22">
         <v>66</v>
       </c>
       <c r="B198" s="6" t="s">
@@ -6469,7 +6469,7 @@
         <v>810</v>
       </c>
       <c r="E198" s="7">
-        <v>32.285714285714285</v>
+        <v>32</v>
       </c>
       <c r="F198" s="6">
         <v>2</v>
@@ -6477,7 +6477,7 @@
       <c r="G198" s="6">
         <v>0</v>
       </c>
-      <c r="H198" s="16">
+      <c r="H198" s="8">
         <v>1</v>
       </c>
       <c r="I198" s="8">
@@ -6485,7 +6485,7 @@
       </c>
     </row>
     <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A199" s="23">
+      <c r="A199" s="22">
         <v>66</v>
       </c>
       <c r="B199" s="6" t="s">
@@ -6498,7 +6498,7 @@
         <v>810</v>
       </c>
       <c r="E199" s="7">
-        <v>34.285714285714285</v>
+        <v>34</v>
       </c>
       <c r="F199" s="6">
         <v>3</v>
@@ -6506,7 +6506,7 @@
       <c r="G199" s="6">
         <v>0</v>
       </c>
-      <c r="H199" s="16">
+      <c r="H199" s="8">
         <v>1</v>
       </c>
       <c r="I199" s="8">
@@ -6514,7 +6514,7 @@
       </c>
     </row>
     <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A200" s="23">
+      <c r="A200" s="22">
         <v>66</v>
       </c>
       <c r="B200" s="6" t="s">
@@ -6527,7 +6527,7 @@
         <v>810</v>
       </c>
       <c r="E200" s="7">
-        <v>36.285714285714285</v>
+        <v>36</v>
       </c>
       <c r="F200" s="6">
         <v>3</v>
@@ -6543,7 +6543,7 @@
       </c>
     </row>
     <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A201" s="23">
+      <c r="A201" s="22">
         <v>66</v>
       </c>
       <c r="B201" s="6" t="s">
@@ -6556,7 +6556,7 @@
         <v>810</v>
       </c>
       <c r="E201" s="7">
-        <v>39.571428571428569</v>
+        <v>40</v>
       </c>
       <c r="F201" s="6">
         <v>3</v>
@@ -6572,7 +6572,7 @@
       </c>
     </row>
     <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A202" s="23">
+      <c r="A202" s="22">
         <v>66</v>
       </c>
       <c r="B202" s="6" t="s">
@@ -6585,7 +6585,7 @@
         <v>810</v>
       </c>
       <c r="E202" s="7">
-        <v>41.571428571428569</v>
+        <v>42</v>
       </c>
       <c r="F202" s="6">
         <v>3</v>
@@ -6593,7 +6593,7 @@
       <c r="G202" s="6">
         <v>0</v>
       </c>
-      <c r="H202" s="16">
+      <c r="H202" s="8">
         <v>1</v>
       </c>
       <c r="I202" s="8">
@@ -6601,7 +6601,7 @@
       </c>
     </row>
     <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A203" s="23">
+      <c r="A203" s="22">
         <v>67</v>
       </c>
       <c r="B203" s="6" t="s">
@@ -6614,7 +6614,7 @@
         <v>2100</v>
       </c>
       <c r="E203" s="7">
-        <v>32.714285714285715</v>
+        <v>33</v>
       </c>
       <c r="F203" s="6">
         <v>0</v>
@@ -6630,7 +6630,7 @@
       </c>
     </row>
     <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A204" s="23">
+      <c r="A204" s="22">
         <v>67</v>
       </c>
       <c r="B204" s="6" t="s">
@@ -6659,7 +6659,7 @@
       </c>
     </row>
     <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="23">
+      <c r="A205" s="22">
         <v>68</v>
       </c>
       <c r="B205" s="6" t="s">
@@ -6672,7 +6672,7 @@
         <v>2210</v>
       </c>
       <c r="E205" s="7">
-        <v>37.857142857142854</v>
+        <v>38</v>
       </c>
       <c r="F205" s="6">
         <v>0</v>
@@ -6688,7 +6688,7 @@
       </c>
     </row>
     <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="23">
+      <c r="A206" s="22">
         <v>68</v>
       </c>
       <c r="B206" s="6" t="s">
@@ -6701,7 +6701,7 @@
         <v>2210</v>
       </c>
       <c r="E206" s="7">
-        <v>42.142857142857146</v>
+        <v>42</v>
       </c>
       <c r="F206" s="6">
         <v>0</v>
@@ -6717,7 +6717,7 @@
       </c>
     </row>
     <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A207" s="23">
+      <c r="A207" s="22">
         <v>69</v>
       </c>
       <c r="B207" s="6" t="s">
@@ -6730,7 +6730,7 @@
         <v>1100</v>
       </c>
       <c r="E207" s="7">
-        <v>32.428571428571431</v>
+        <v>32</v>
       </c>
       <c r="F207" s="6">
         <v>1</v>
@@ -6746,7 +6746,7 @@
       </c>
     </row>
     <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A208" s="23">
+      <c r="A208" s="22">
         <v>69</v>
       </c>
       <c r="B208" s="6" t="s">
@@ -6759,7 +6759,7 @@
         <v>1100</v>
       </c>
       <c r="E208" s="7">
-        <v>34.142857142857146</v>
+        <v>34</v>
       </c>
       <c r="F208" s="6">
         <v>1</v>
@@ -6775,7 +6775,7 @@
       </c>
     </row>
     <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A209" s="23">
+      <c r="A209" s="22">
         <v>69</v>
       </c>
       <c r="B209" s="6" t="s">
@@ -6796,7 +6796,7 @@
       <c r="G209" s="6">
         <v>0</v>
       </c>
-      <c r="H209" s="16">
+      <c r="H209" s="8">
         <v>1</v>
       </c>
       <c r="I209" s="8">
@@ -6804,7 +6804,7 @@
       </c>
     </row>
     <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A210" s="23">
+      <c r="A210" s="22">
         <v>69</v>
       </c>
       <c r="B210" s="6" t="s">
@@ -6817,7 +6817,7 @@
         <v>1100</v>
       </c>
       <c r="E210" s="7">
-        <v>43.428571428571431</v>
+        <v>43</v>
       </c>
       <c r="F210" s="6">
         <v>9</v>
@@ -6833,7 +6833,7 @@
       </c>
     </row>
     <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A211" s="23">
+      <c r="A211" s="22">
         <v>70</v>
       </c>
       <c r="B211" s="6" t="s">
@@ -6846,7 +6846,7 @@
         <v>1830</v>
       </c>
       <c r="E211" s="7">
-        <v>32.857142857142854</v>
+        <v>33</v>
       </c>
       <c r="F211" s="6">
         <v>0</v>
@@ -6862,7 +6862,7 @@
       </c>
     </row>
     <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A212" s="23">
+      <c r="A212" s="22">
         <v>70</v>
       </c>
       <c r="B212" s="6" t="s">
@@ -6875,7 +6875,7 @@
         <v>1830</v>
       </c>
       <c r="E212" s="7">
-        <v>34.857142857142854</v>
+        <v>35</v>
       </c>
       <c r="F212" s="6">
         <v>0</v>
@@ -6891,7 +6891,7 @@
       </c>
     </row>
     <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A213" s="23">
+      <c r="A213" s="22">
         <v>70</v>
       </c>
       <c r="B213" s="6" t="s">
@@ -6904,7 +6904,7 @@
         <v>1830</v>
       </c>
       <c r="E213" s="7">
-        <v>37.142857142857146</v>
+        <v>37</v>
       </c>
       <c r="F213" s="6">
         <v>0</v>
@@ -6920,7 +6920,7 @@
       </c>
     </row>
     <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A214" s="23">
+      <c r="A214" s="22">
         <v>70</v>
       </c>
       <c r="B214" s="6" t="s">
@@ -6933,7 +6933,7 @@
         <v>1830</v>
       </c>
       <c r="E214" s="7">
-        <v>40.142857142857139</v>
+        <v>40</v>
       </c>
       <c r="F214" s="6">
         <v>0</v>
@@ -6949,7 +6949,7 @@
       </c>
     </row>
     <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A215" s="23">
+      <c r="A215" s="22">
         <v>71</v>
       </c>
       <c r="B215" s="6" t="s">
@@ -6962,7 +6962,7 @@
         <v>1660</v>
       </c>
       <c r="E215" s="7">
-        <v>32.857142857142854</v>
+        <v>33</v>
       </c>
       <c r="F215" s="6">
         <v>0</v>
@@ -6978,7 +6978,7 @@
       </c>
     </row>
     <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A216" s="23">
+      <c r="A216" s="22">
         <v>71</v>
       </c>
       <c r="B216" s="6" t="s">
@@ -6991,7 +6991,7 @@
         <v>1660</v>
       </c>
       <c r="E216" s="7">
-        <v>34.857142857142854</v>
+        <v>35</v>
       </c>
       <c r="F216" s="6">
         <v>0</v>
@@ -7007,7 +7007,7 @@
       </c>
     </row>
     <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A217" s="23">
+      <c r="A217" s="22">
         <v>71</v>
       </c>
       <c r="B217" s="6" t="s">
@@ -7020,7 +7020,7 @@
         <v>1660</v>
       </c>
       <c r="E217" s="7">
-        <v>37.142857142857146</v>
+        <v>37</v>
       </c>
       <c r="F217" s="6">
         <v>0</v>
@@ -7036,7 +7036,7 @@
       </c>
     </row>
     <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A218" s="23">
+      <c r="A218" s="22">
         <v>71</v>
       </c>
       <c r="B218" s="6" t="s">
@@ -7049,7 +7049,7 @@
         <v>1660</v>
       </c>
       <c r="E218" s="7">
-        <v>40.142857142857139</v>
+        <v>40</v>
       </c>
       <c r="F218" s="6">
         <v>0</v>
@@ -7065,7 +7065,7 @@
       </c>
     </row>
     <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A219" s="23">
+      <c r="A219" s="22">
         <v>72</v>
       </c>
       <c r="B219" s="6" t="s">
@@ -7078,7 +7078,7 @@
         <v>1490</v>
       </c>
       <c r="E219" s="7">
-        <v>37.142857142857146</v>
+        <v>37</v>
       </c>
       <c r="F219" s="6">
         <v>0</v>
@@ -7094,7 +7094,7 @@
       </c>
     </row>
     <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="23">
+      <c r="A220" s="22">
         <v>73</v>
       </c>
       <c r="B220" s="6" t="s">
@@ -7107,7 +7107,7 @@
         <v>1490</v>
       </c>
       <c r="E220" s="7">
-        <v>37.714285714285715</v>
+        <v>38</v>
       </c>
       <c r="F220" s="6">
         <v>0</v>
@@ -7123,7 +7123,7 @@
       </c>
     </row>
     <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="23">
+      <c r="A221" s="22">
         <v>74</v>
       </c>
       <c r="B221" s="6" t="s">
@@ -7136,7 +7136,7 @@
         <v>1440</v>
       </c>
       <c r="E221" s="7">
-        <v>37.714285714285715</v>
+        <v>38</v>
       </c>
       <c r="F221" s="6">
         <v>0</v>
@@ -7152,7 +7152,7 @@
       </c>
     </row>
     <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A222" s="23">
+      <c r="A222" s="22">
         <v>75</v>
       </c>
       <c r="B222" s="6" t="s">
@@ -7165,7 +7165,7 @@
         <v>1240</v>
       </c>
       <c r="E222" s="7">
-        <v>37.714285714285715</v>
+        <v>38</v>
       </c>
       <c r="F222" s="6">
         <v>0</v>
@@ -7181,7 +7181,7 @@
       </c>
     </row>
     <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A223" s="23">
+      <c r="A223" s="22">
         <v>76</v>
       </c>
       <c r="B223" s="6" t="s">
@@ -7194,7 +7194,7 @@
         <v>1470</v>
       </c>
       <c r="E223" s="7">
-        <v>35.142857142857146</v>
+        <v>35</v>
       </c>
       <c r="F223" s="6">
         <v>0</v>
@@ -7210,7 +7210,7 @@
       </c>
     </row>
     <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A224" s="23">
+      <c r="A224" s="22">
         <v>76</v>
       </c>
       <c r="B224" s="6" t="s">
@@ -7223,7 +7223,7 @@
         <v>1470</v>
       </c>
       <c r="E224" s="7">
-        <v>37.142857142857146</v>
+        <v>37</v>
       </c>
       <c r="F224" s="6">
         <v>0</v>
@@ -7239,7 +7239,7 @@
       </c>
     </row>
     <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A225" s="23">
+      <c r="A225" s="22">
         <v>76</v>
       </c>
       <c r="B225" s="6" t="s">
@@ -7252,7 +7252,7 @@
         <v>1470</v>
       </c>
       <c r="E225" s="7">
-        <v>40.142857142857146</v>
+        <v>40</v>
       </c>
       <c r="F225" s="6">
         <v>0</v>
@@ -7268,7 +7268,7 @@
       </c>
     </row>
     <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A226" s="23">
+      <c r="A226" s="22">
         <v>77</v>
       </c>
       <c r="B226" s="6" t="s">
@@ -7281,7 +7281,7 @@
         <v>790</v>
       </c>
       <c r="E226" s="7">
-        <v>32.571428571428569</v>
+        <v>33</v>
       </c>
       <c r="F226" s="6">
         <v>0</v>
@@ -7297,7 +7297,7 @@
       </c>
     </row>
     <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A227" s="23">
+      <c r="A227" s="22">
         <v>77</v>
       </c>
       <c r="B227" s="6" t="s">
@@ -7310,7 +7310,7 @@
         <v>790</v>
       </c>
       <c r="E227" s="7">
-        <v>34.571428571428569</v>
+        <v>35</v>
       </c>
       <c r="F227" s="6">
         <v>0</v>
@@ -7326,7 +7326,7 @@
       </c>
     </row>
     <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A228" s="23">
+      <c r="A228" s="22">
         <v>77</v>
       </c>
       <c r="B228" s="6" t="s">
@@ -7339,7 +7339,7 @@
         <v>790</v>
       </c>
       <c r="E228" s="7">
-        <v>36.857142857142861</v>
+        <v>37</v>
       </c>
       <c r="F228" s="6">
         <v>0</v>
@@ -7355,7 +7355,7 @@
       </c>
     </row>
     <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A229" s="23">
+      <c r="A229" s="22">
         <v>78</v>
       </c>
       <c r="B229" s="6" t="s">
@@ -7368,7 +7368,7 @@
         <v>1330</v>
       </c>
       <c r="E229" s="7">
-        <v>36.714285714285715</v>
+        <v>37</v>
       </c>
       <c r="F229" s="6">
         <v>0</v>
@@ -7384,7 +7384,7 @@
       </c>
     </row>
     <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A230" s="23">
+      <c r="A230" s="22">
         <v>79</v>
       </c>
       <c r="B230" s="6" t="s">
@@ -7397,7 +7397,7 @@
         <v>1760</v>
       </c>
       <c r="E230" s="7">
-        <v>39.714285714285715</v>
+        <v>40</v>
       </c>
       <c r="F230" s="6">
         <v>0</v>
@@ -7413,7 +7413,7 @@
       </c>
     </row>
     <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A231" s="23">
+      <c r="A231" s="22">
         <v>80</v>
       </c>
       <c r="B231" s="6" t="s">
@@ -7426,7 +7426,7 @@
         <v>2400</v>
       </c>
       <c r="E231" s="7">
-        <v>41.142857142857146</v>
+        <v>41</v>
       </c>
       <c r="F231" s="6">
         <v>0</v>
@@ -7442,7 +7442,7 @@
       </c>
     </row>
     <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A232" s="22">
+      <c r="A232" s="21">
         <v>81</v>
       </c>
       <c r="B232" s="6" t="s">
@@ -7470,37 +7470,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:9" s="21" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A233" s="23">
+    <row r="233" spans="1:9" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A233" s="22">
         <v>82</v>
       </c>
-      <c r="B233" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C233" s="18">
+      <c r="B233" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C233" s="17">
         <v>39</v>
       </c>
-      <c r="D233" s="18">
+      <c r="D233" s="17">
         <v>3200</v>
       </c>
-      <c r="E233" s="18">
+      <c r="E233" s="17">
         <v>40</v>
       </c>
-      <c r="F233" s="19">
-        <v>0</v>
-      </c>
-      <c r="G233" s="19">
-        <v>0</v>
-      </c>
-      <c r="H233" s="20">
-        <v>2</v>
-      </c>
-      <c r="I233" s="20">
+      <c r="F233" s="18">
+        <v>0</v>
+      </c>
+      <c r="G233" s="18">
+        <v>0</v>
+      </c>
+      <c r="H233" s="19">
+        <v>2</v>
+      </c>
+      <c r="I233" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A234" s="23">
+      <c r="A234" s="22">
         <v>83</v>
       </c>
       <c r="B234" s="5" t="s">
@@ -7529,7 +7529,7 @@
       </c>
     </row>
     <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" s="23">
+      <c r="A235" s="22">
         <v>83</v>
       </c>
       <c r="B235" s="5" t="s">
@@ -7558,7 +7558,7 @@
       </c>
     </row>
     <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="23">
+      <c r="A236" s="22">
         <v>83</v>
       </c>
       <c r="B236" s="5" t="s">
@@ -7587,7 +7587,7 @@
       </c>
     </row>
     <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A237" s="23">
+      <c r="A237" s="22">
         <v>83</v>
       </c>
       <c r="B237" s="5" t="s">
@@ -7616,7 +7616,7 @@
       </c>
     </row>
     <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A238" s="23">
+      <c r="A238" s="22">
         <v>84</v>
       </c>
       <c r="B238" s="5" t="s">
@@ -7645,7 +7645,7 @@
       </c>
     </row>
     <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A239" s="23">
+      <c r="A239" s="22">
         <v>84</v>
       </c>
       <c r="B239" s="5" t="s">
@@ -7674,7 +7674,7 @@
       </c>
     </row>
     <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A240" s="23">
+      <c r="A240" s="22">
         <v>84</v>
       </c>
       <c r="B240" s="5" t="s">
@@ -7703,7 +7703,7 @@
       </c>
     </row>
     <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A241" s="23">
+      <c r="A241" s="22">
         <v>84</v>
       </c>
       <c r="B241" s="5" t="s">
@@ -7732,7 +7732,7 @@
       </c>
     </row>
     <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A242" s="23">
+      <c r="A242" s="22">
         <v>84</v>
       </c>
       <c r="B242" s="5" t="s">
@@ -7761,7 +7761,7 @@
       </c>
     </row>
     <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A243" s="23">
+      <c r="A243" s="22">
         <v>84</v>
       </c>
       <c r="B243" s="5" t="s">
@@ -7790,7 +7790,7 @@
       </c>
     </row>
     <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A244" s="23">
+      <c r="A244" s="22">
         <v>85</v>
       </c>
       <c r="B244" s="5" t="s">
@@ -7819,7 +7819,7 @@
       </c>
     </row>
     <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A245" s="23">
+      <c r="A245" s="22">
         <v>85</v>
       </c>
       <c r="B245" s="5" t="s">
@@ -7848,7 +7848,7 @@
       </c>
     </row>
     <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A246" s="23">
+      <c r="A246" s="22">
         <v>85</v>
       </c>
       <c r="B246" s="5" t="s">
@@ -7877,7 +7877,7 @@
       </c>
     </row>
     <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A247" s="23">
+      <c r="A247" s="22">
         <v>85</v>
       </c>
       <c r="B247" s="5" t="s">
@@ -7906,7 +7906,7 @@
       </c>
     </row>
     <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A248" s="23">
+      <c r="A248" s="22">
         <v>86</v>
       </c>
       <c r="B248" s="5" t="s">
@@ -7935,7 +7935,7 @@
       </c>
     </row>
     <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A249" s="23">
+      <c r="A249" s="22">
         <v>87</v>
       </c>
       <c r="B249" s="5" t="s">
@@ -7964,7 +7964,7 @@
       </c>
     </row>
     <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A250" s="23">
+      <c r="A250" s="22">
         <v>87</v>
       </c>
       <c r="B250" s="5" t="s">
@@ -7993,7 +7993,7 @@
       </c>
     </row>
     <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A251" s="23">
+      <c r="A251" s="22">
         <v>88</v>
       </c>
       <c r="B251" s="5" t="s">
@@ -8022,7 +8022,7 @@
       </c>
     </row>
     <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A252" s="23">
+      <c r="A252" s="22">
         <v>89</v>
       </c>
       <c r="B252" s="5" t="s">
@@ -8051,7 +8051,7 @@
       </c>
     </row>
     <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A253" s="23">
+      <c r="A253" s="22">
         <v>89</v>
       </c>
       <c r="B253" s="5" t="s">
@@ -8080,7 +8080,7 @@
       </c>
     </row>
     <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A254" s="23">
+      <c r="A254" s="22">
         <v>89</v>
       </c>
       <c r="B254" s="5" t="s">
@@ -8109,7 +8109,7 @@
       </c>
     </row>
     <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A255" s="23">
+      <c r="A255" s="22">
         <v>90</v>
       </c>
       <c r="B255" s="5" t="s">
@@ -8138,7 +8138,7 @@
       </c>
     </row>
     <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A256" s="23">
+      <c r="A256" s="22">
         <v>90</v>
       </c>
       <c r="B256" s="5" t="s">
@@ -8167,7 +8167,7 @@
       </c>
     </row>
     <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A257" s="23">
+      <c r="A257" s="22">
         <v>91</v>
       </c>
       <c r="B257" s="5" t="s">
@@ -8196,7 +8196,7 @@
       </c>
     </row>
     <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A258" s="23">
+      <c r="A258" s="22">
         <v>91</v>
       </c>
       <c r="B258" s="5" t="s">
@@ -8225,7 +8225,7 @@
       </c>
     </row>
     <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A259" s="23">
+      <c r="A259" s="22">
         <v>91</v>
       </c>
       <c r="B259" s="5" t="s">
@@ -8254,7 +8254,7 @@
       </c>
     </row>
     <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A260" s="23">
+      <c r="A260" s="22">
         <v>91</v>
       </c>
       <c r="B260" s="5" t="s">
@@ -8283,7 +8283,7 @@
       </c>
     </row>
     <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A261" s="23">
+      <c r="A261" s="22">
         <v>91</v>
       </c>
       <c r="B261" s="5" t="s">
@@ -8312,7 +8312,7 @@
       </c>
     </row>
     <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A262" s="23">
+      <c r="A262" s="22">
         <v>92</v>
       </c>
       <c r="B262" s="5" t="s">
@@ -8341,7 +8341,7 @@
       </c>
     </row>
     <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A263" s="23">
+      <c r="A263" s="22">
         <v>92</v>
       </c>
       <c r="B263" s="5" t="s">
@@ -8370,7 +8370,7 @@
       </c>
     </row>
     <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A264" s="23">
+      <c r="A264" s="22">
         <v>92</v>
       </c>
       <c r="B264" s="5" t="s">
@@ -8399,7 +8399,7 @@
       </c>
     </row>
     <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A265" s="23">
+      <c r="A265" s="22">
         <v>92</v>
       </c>
       <c r="B265" s="5" t="s">
@@ -8428,7 +8428,7 @@
       </c>
     </row>
     <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A266" s="23">
+      <c r="A266" s="22">
         <v>92</v>
       </c>
       <c r="B266" s="5" t="s">
@@ -8457,7 +8457,7 @@
       </c>
     </row>
     <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A267" s="23">
+      <c r="A267" s="22">
         <v>93</v>
       </c>
       <c r="B267" s="5" t="s">
@@ -8486,7 +8486,7 @@
       </c>
     </row>
     <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A268" s="23">
+      <c r="A268" s="22">
         <v>93</v>
       </c>
       <c r="B268" s="5" t="s">
@@ -8515,7 +8515,7 @@
       </c>
     </row>
     <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A269" s="23">
+      <c r="A269" s="22">
         <v>93</v>
       </c>
       <c r="B269" s="5" t="s">
@@ -8544,7 +8544,7 @@
       </c>
     </row>
     <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A270" s="23">
+      <c r="A270" s="22">
         <v>93</v>
       </c>
       <c r="B270" s="5" t="s">
@@ -8573,7 +8573,7 @@
       </c>
     </row>
     <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A271" s="23">
+      <c r="A271" s="22">
         <v>94</v>
       </c>
       <c r="B271" s="5" t="s">
@@ -8602,7 +8602,7 @@
       </c>
     </row>
     <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A272" s="23">
+      <c r="A272" s="22">
         <v>94</v>
       </c>
       <c r="B272" s="5" t="s">
@@ -8631,7 +8631,7 @@
       </c>
     </row>
     <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A273" s="23">
+      <c r="A273" s="22">
         <v>95</v>
       </c>
       <c r="B273" s="5" t="s">
@@ -8660,7 +8660,7 @@
       </c>
     </row>
     <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A274" s="23">
+      <c r="A274" s="22">
         <v>95</v>
       </c>
       <c r="B274" s="5" t="s">
@@ -8689,7 +8689,7 @@
       </c>
     </row>
     <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A275" s="23">
+      <c r="A275" s="22">
         <v>95</v>
       </c>
       <c r="B275" s="5" t="s">
@@ -8718,7 +8718,7 @@
       </c>
     </row>
     <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A276" s="23">
+      <c r="A276" s="22">
         <v>96</v>
       </c>
       <c r="B276" s="5" t="s">
@@ -8747,7 +8747,7 @@
       </c>
     </row>
     <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A277" s="23">
+      <c r="A277" s="22">
         <v>96</v>
       </c>
       <c r="B277" s="5" t="s">
@@ -8776,7 +8776,7 @@
       </c>
     </row>
     <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A278" s="23">
+      <c r="A278" s="22">
         <v>96</v>
       </c>
       <c r="B278" s="5" t="s">
@@ -8805,7 +8805,7 @@
       </c>
     </row>
     <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A279" s="23">
+      <c r="A279" s="22">
         <v>96</v>
       </c>
       <c r="B279" s="5" t="s">
@@ -8834,7 +8834,7 @@
       </c>
     </row>
     <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A280" s="23">
+      <c r="A280" s="22">
         <v>97</v>
       </c>
       <c r="B280" s="5" t="s">
@@ -8863,7 +8863,7 @@
       </c>
     </row>
     <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A281" s="23">
+      <c r="A281" s="22">
         <v>97</v>
       </c>
       <c r="B281" s="5" t="s">
@@ -8892,7 +8892,7 @@
       </c>
     </row>
     <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A282" s="23">
+      <c r="A282" s="22">
         <v>97</v>
       </c>
       <c r="B282" s="5" t="s">
@@ -8921,7 +8921,7 @@
       </c>
     </row>
     <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A283" s="23">
+      <c r="A283" s="22">
         <v>97</v>
       </c>
       <c r="B283" s="5" t="s">
@@ -8950,7 +8950,7 @@
       </c>
     </row>
     <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A284" s="23">
+      <c r="A284" s="22">
         <v>98</v>
       </c>
       <c r="B284" s="5" t="s">
@@ -8979,7 +8979,7 @@
       </c>
     </row>
     <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A285" s="23">
+      <c r="A285" s="22">
         <v>98</v>
       </c>
       <c r="B285" s="5" t="s">
@@ -9008,7 +9008,7 @@
       </c>
     </row>
     <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A286" s="23">
+      <c r="A286" s="22">
         <v>98</v>
       </c>
       <c r="B286" s="5" t="s">
@@ -9037,7 +9037,7 @@
       </c>
     </row>
     <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A287" s="23">
+      <c r="A287" s="22">
         <v>98</v>
       </c>
       <c r="B287" s="5" t="s">
@@ -9066,7 +9066,7 @@
       </c>
     </row>
     <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A288" s="23">
+      <c r="A288" s="22">
         <v>98</v>
       </c>
       <c r="B288" s="5" t="s">
@@ -9095,7 +9095,7 @@
       </c>
     </row>
     <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A289" s="23">
+      <c r="A289" s="22">
         <v>99</v>
       </c>
       <c r="B289" s="5" t="s">
@@ -9124,7 +9124,7 @@
       </c>
     </row>
     <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A290" s="23">
+      <c r="A290" s="22">
         <v>99</v>
       </c>
       <c r="B290" s="5" t="s">
@@ -9153,7 +9153,7 @@
       </c>
     </row>
     <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A291" s="23">
+      <c r="A291" s="22">
         <v>99</v>
       </c>
       <c r="B291" s="5" t="s">
@@ -9182,7 +9182,7 @@
       </c>
     </row>
     <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A292" s="23">
+      <c r="A292" s="22">
         <v>99</v>
       </c>
       <c r="B292" s="5" t="s">
@@ -9211,7 +9211,7 @@
       </c>
     </row>
     <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A293" s="23">
+      <c r="A293" s="22">
         <v>100</v>
       </c>
       <c r="B293" s="5" t="s">
@@ -9240,7 +9240,7 @@
       </c>
     </row>
     <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A294" s="23">
+      <c r="A294" s="22">
         <v>100</v>
       </c>
       <c r="B294" s="5" t="s">
@@ -9269,7 +9269,7 @@
       </c>
     </row>
     <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A295" s="23">
+      <c r="A295" s="22">
         <v>100</v>
       </c>
       <c r="B295" s="5" t="s">
@@ -9298,7 +9298,7 @@
       </c>
     </row>
     <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A296" s="23">
+      <c r="A296" s="22">
         <v>101</v>
       </c>
       <c r="B296" s="5" t="s">
@@ -9327,7 +9327,7 @@
       </c>
     </row>
     <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A297" s="23">
+      <c r="A297" s="22">
         <v>101</v>
       </c>
       <c r="B297" s="5" t="s">
@@ -9356,7 +9356,7 @@
       </c>
     </row>
     <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A298" s="23">
+      <c r="A298" s="22">
         <v>101</v>
       </c>
       <c r="B298" s="5" t="s">
@@ -9385,7 +9385,7 @@
       </c>
     </row>
     <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A299" s="23">
+      <c r="A299" s="22">
         <v>102</v>
       </c>
       <c r="B299" s="5" t="s">
@@ -9414,7 +9414,7 @@
       </c>
     </row>
     <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A300" s="23">
+      <c r="A300" s="22">
         <v>102</v>
       </c>
       <c r="B300" s="5" t="s">
@@ -9443,7 +9443,7 @@
       </c>
     </row>
     <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A301" s="23">
+      <c r="A301" s="22">
         <v>102</v>
       </c>
       <c r="B301" s="5" t="s">
@@ -9472,7 +9472,7 @@
       </c>
     </row>
     <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A302" s="23">
+      <c r="A302" s="22">
         <v>103</v>
       </c>
       <c r="B302" s="5" t="s">
@@ -9501,7 +9501,7 @@
       </c>
     </row>
     <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A303" s="23">
+      <c r="A303" s="22">
         <v>103</v>
       </c>
       <c r="B303" s="5" t="s">
@@ -9530,7 +9530,7 @@
       </c>
     </row>
     <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A304" s="23">
+      <c r="A304" s="22">
         <v>103</v>
       </c>
       <c r="B304" s="5" t="s">
@@ -9559,7 +9559,7 @@
       </c>
     </row>
     <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A305" s="23">
+      <c r="A305" s="22">
         <v>103</v>
       </c>
       <c r="B305" s="5" t="s">
@@ -9588,7 +9588,7 @@
       </c>
     </row>
     <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A306" s="23">
+      <c r="A306" s="22">
         <v>103</v>
       </c>
       <c r="B306" s="5" t="s">
@@ -9617,7 +9617,7 @@
       </c>
     </row>
     <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A307" s="23">
+      <c r="A307" s="22">
         <v>104</v>
       </c>
       <c r="B307" s="5" t="s">
@@ -9646,7 +9646,7 @@
       </c>
     </row>
     <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A308" s="23">
+      <c r="A308" s="22">
         <v>104</v>
       </c>
       <c r="B308" s="5" t="s">
@@ -9675,7 +9675,7 @@
       </c>
     </row>
     <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A309" s="23">
+      <c r="A309" s="22">
         <v>104</v>
       </c>
       <c r="B309" s="5" t="s">
@@ -9704,7 +9704,7 @@
       </c>
     </row>
     <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A310" s="23">
+      <c r="A310" s="22">
         <v>104</v>
       </c>
       <c r="B310" s="5" t="s">
@@ -9733,7 +9733,7 @@
       </c>
     </row>
     <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A311" s="23">
+      <c r="A311" s="22">
         <v>105</v>
       </c>
       <c r="B311" s="5" t="s">
@@ -9762,7 +9762,7 @@
       </c>
     </row>
     <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A312" s="23">
+      <c r="A312" s="22">
         <v>106</v>
       </c>
       <c r="B312" s="5" t="s">
@@ -9791,7 +9791,7 @@
       </c>
     </row>
     <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A313" s="23">
+      <c r="A313" s="22">
         <v>107</v>
       </c>
       <c r="B313" s="5" t="s">
@@ -9820,7 +9820,7 @@
       </c>
     </row>
     <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A314" s="23">
+      <c r="A314" s="22">
         <v>107</v>
       </c>
       <c r="B314" s="5" t="s">
@@ -9849,7 +9849,7 @@
       </c>
     </row>
     <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A315" s="23">
+      <c r="A315" s="22">
         <v>108</v>
       </c>
       <c r="B315" s="5" t="s">
@@ -9878,7 +9878,7 @@
       </c>
     </row>
     <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A316" s="23">
+      <c r="A316" s="22">
         <v>109</v>
       </c>
       <c r="B316" s="5" t="s">
@@ -9907,7 +9907,7 @@
       </c>
     </row>
     <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A317" s="23">
+      <c r="A317" s="22">
         <v>110</v>
       </c>
       <c r="B317" s="5" t="s">
@@ -9936,7 +9936,7 @@
       </c>
     </row>
     <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A318" s="23">
+      <c r="A318" s="22">
         <v>111</v>
       </c>
       <c r="B318" s="5" t="s">
@@ -9965,7 +9965,7 @@
       </c>
     </row>
     <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A319" s="23">
+      <c r="A319" s="22">
         <v>111</v>
       </c>
       <c r="B319" s="5" t="s">
@@ -9994,7 +9994,7 @@
       </c>
     </row>
     <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A320" s="23">
+      <c r="A320" s="22">
         <v>111</v>
       </c>
       <c r="B320" s="5" t="s">
@@ -10023,7 +10023,7 @@
       </c>
     </row>
     <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A321" s="23">
+      <c r="A321" s="22">
         <v>111</v>
       </c>
       <c r="B321" s="5" t="s">
@@ -10052,7 +10052,7 @@
       </c>
     </row>
     <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A322" s="23">
+      <c r="A322" s="22">
         <v>111</v>
       </c>
       <c r="B322" s="5" t="s">
@@ -10081,7 +10081,7 @@
       </c>
     </row>
     <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A323" s="23">
+      <c r="A323" s="22">
         <v>112</v>
       </c>
       <c r="B323" s="5" t="s">
@@ -10110,7 +10110,7 @@
       </c>
     </row>
     <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A324" s="23">
+      <c r="A324" s="22">
         <v>112</v>
       </c>
       <c r="B324" s="5" t="s">
@@ -10139,7 +10139,7 @@
       </c>
     </row>
     <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A325" s="23">
+      <c r="A325" s="22">
         <v>112</v>
       </c>
       <c r="B325" s="5" t="s">
@@ -10168,7 +10168,7 @@
       </c>
     </row>
     <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A326" s="23">
+      <c r="A326" s="22">
         <v>112</v>
       </c>
       <c r="B326" s="5" t="s">
@@ -10197,7 +10197,7 @@
       </c>
     </row>
     <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A327" s="23">
+      <c r="A327" s="22">
         <v>112</v>
       </c>
       <c r="B327" s="5" t="s">
@@ -10226,7 +10226,7 @@
       </c>
     </row>
     <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A328" s="23">
+      <c r="A328" s="22">
         <v>113</v>
       </c>
       <c r="B328" s="5" t="s">
@@ -10255,7 +10255,7 @@
       </c>
     </row>
     <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A329" s="23">
+      <c r="A329" s="22">
         <v>114</v>
       </c>
       <c r="B329" s="5" t="s">
@@ -10284,7 +10284,7 @@
       </c>
     </row>
     <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A330" s="23">
+      <c r="A330" s="22">
         <v>115</v>
       </c>
       <c r="B330" s="5" t="s">
@@ -10313,7 +10313,7 @@
       </c>
     </row>
     <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A331" s="23">
+      <c r="A331" s="22">
         <v>115</v>
       </c>
       <c r="B331" s="5" t="s">
@@ -10342,7 +10342,7 @@
       </c>
     </row>
     <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A332" s="23">
+      <c r="A332" s="22">
         <v>115</v>
       </c>
       <c r="B332" s="5" t="s">
@@ -10371,7 +10371,7 @@
       </c>
     </row>
     <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A333" s="23">
+      <c r="A333" s="22">
         <v>115</v>
       </c>
       <c r="B333" s="5" t="s">
@@ -10400,7 +10400,7 @@
       </c>
     </row>
     <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A334" s="23">
+      <c r="A334" s="22">
         <v>115</v>
       </c>
       <c r="B334" s="5" t="s">
@@ -10429,7 +10429,7 @@
       </c>
     </row>
     <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A335" s="23">
+      <c r="A335" s="22">
         <v>116</v>
       </c>
       <c r="B335" s="5" t="s">
@@ -10458,7 +10458,7 @@
       </c>
     </row>
     <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A336" s="23">
+      <c r="A336" s="22">
         <v>117</v>
       </c>
       <c r="B336" s="5" t="s">
@@ -10487,7 +10487,7 @@
       </c>
     </row>
     <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A337" s="23">
+      <c r="A337" s="22">
         <v>117</v>
       </c>
       <c r="B337" s="5" t="s">
@@ -10516,7 +10516,7 @@
       </c>
     </row>
     <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A338" s="23">
+      <c r="A338" s="22">
         <v>117</v>
       </c>
       <c r="B338" s="5" t="s">
@@ -10545,7 +10545,7 @@
       </c>
     </row>
     <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A339" s="23">
+      <c r="A339" s="22">
         <v>117</v>
       </c>
       <c r="B339" s="5" t="s">
@@ -10574,7 +10574,7 @@
       </c>
     </row>
     <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A340" s="23">
+      <c r="A340" s="22">
         <v>118</v>
       </c>
       <c r="B340" s="5" t="s">
@@ -10603,7 +10603,7 @@
       </c>
     </row>
     <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A341" s="23">
+      <c r="A341" s="22">
         <v>118</v>
       </c>
       <c r="B341" s="5" t="s">
@@ -10632,7 +10632,7 @@
       </c>
     </row>
     <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A342" s="23">
+      <c r="A342" s="22">
         <v>118</v>
       </c>
       <c r="B342" s="5" t="s">
@@ -10661,7 +10661,7 @@
       </c>
     </row>
     <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A343" s="23">
+      <c r="A343" s="22">
         <v>118</v>
       </c>
       <c r="B343" s="5" t="s">
@@ -10690,7 +10690,7 @@
       </c>
     </row>
     <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A344" s="23">
+      <c r="A344" s="22">
         <v>119</v>
       </c>
       <c r="B344" s="5" t="s">
@@ -10719,7 +10719,7 @@
       </c>
     </row>
     <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A345" s="23">
+      <c r="A345" s="22">
         <v>119</v>
       </c>
       <c r="B345" s="5" t="s">
@@ -10748,7 +10748,7 @@
       </c>
     </row>
     <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A346" s="23">
+      <c r="A346" s="22">
         <v>119</v>
       </c>
       <c r="B346" s="5" t="s">
@@ -10777,7 +10777,7 @@
       </c>
     </row>
     <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A347" s="23">
+      <c r="A347" s="22">
         <v>119</v>
       </c>
       <c r="B347" s="5" t="s">
@@ -10806,7 +10806,7 @@
       </c>
     </row>
     <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A348" s="23">
+      <c r="A348" s="22">
         <v>120</v>
       </c>
       <c r="B348" s="5" t="s">
@@ -10835,7 +10835,7 @@
       </c>
     </row>
     <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A349" s="23">
+      <c r="A349" s="22">
         <v>120</v>
       </c>
       <c r="B349" s="5" t="s">
@@ -10864,7 +10864,7 @@
       </c>
     </row>
     <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A350" s="23">
+      <c r="A350" s="22">
         <v>120</v>
       </c>
       <c r="B350" s="5" t="s">
@@ -10893,7 +10893,7 @@
       </c>
     </row>
     <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A351" s="23">
+      <c r="A351" s="22">
         <v>121</v>
       </c>
       <c r="B351" s="5" t="s">
@@ -10922,7 +10922,7 @@
       </c>
     </row>
     <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A352" s="23">
+      <c r="A352" s="22">
         <v>121</v>
       </c>
       <c r="B352" s="5" t="s">
@@ -10951,7 +10951,7 @@
       </c>
     </row>
     <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A353" s="23">
+      <c r="A353" s="22">
         <v>121</v>
       </c>
       <c r="B353" s="5" t="s">
@@ -10980,7 +10980,7 @@
       </c>
     </row>
     <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A354" s="23">
+      <c r="A354" s="22">
         <v>121</v>
       </c>
       <c r="B354" s="5" t="s">
@@ -11009,7 +11009,7 @@
       </c>
     </row>
     <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A355" s="23">
+      <c r="A355" s="22">
         <v>122</v>
       </c>
       <c r="B355" s="5" t="s">
@@ -11038,7 +11038,7 @@
       </c>
     </row>
     <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A356" s="23">
+      <c r="A356" s="22">
         <v>122</v>
       </c>
       <c r="B356" s="5" t="s">
@@ -11067,7 +11067,7 @@
       </c>
     </row>
     <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A357" s="23">
+      <c r="A357" s="22">
         <v>122</v>
       </c>
       <c r="B357" s="5" t="s">
@@ -11096,7 +11096,7 @@
       </c>
     </row>
     <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A358" s="23">
+      <c r="A358" s="22">
         <v>123</v>
       </c>
       <c r="B358" s="5" t="s">
@@ -11125,7 +11125,7 @@
       </c>
     </row>
     <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A359" s="23">
+      <c r="A359" s="22">
         <v>123</v>
       </c>
       <c r="B359" s="5" t="s">
@@ -11154,7 +11154,7 @@
       </c>
     </row>
     <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A360" s="23">
+      <c r="A360" s="22">
         <v>123</v>
       </c>
       <c r="B360" s="5" t="s">
@@ -11183,7 +11183,7 @@
       </c>
     </row>
     <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A361" s="23">
+      <c r="A361" s="22">
         <v>123</v>
       </c>
       <c r="B361" s="5" t="s">
@@ -11212,7 +11212,7 @@
       </c>
     </row>
     <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A362" s="23">
+      <c r="A362" s="22">
         <v>123</v>
       </c>
       <c r="B362" s="5" t="s">
@@ -11241,7 +11241,7 @@
       </c>
     </row>
     <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A363" s="23">
+      <c r="A363" s="22">
         <v>124</v>
       </c>
       <c r="B363" s="5" t="s">
@@ -11270,7 +11270,7 @@
       </c>
     </row>
     <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A364" s="23">
+      <c r="A364" s="22">
         <v>124</v>
       </c>
       <c r="B364" s="5" t="s">
@@ -11299,7 +11299,7 @@
       </c>
     </row>
     <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A365" s="23">
+      <c r="A365" s="22">
         <v>124</v>
       </c>
       <c r="B365" s="5" t="s">
@@ -11328,7 +11328,7 @@
       </c>
     </row>
     <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A366" s="23">
+      <c r="A366" s="22">
         <v>124</v>
       </c>
       <c r="B366" s="5" t="s">
@@ -11357,7 +11357,7 @@
       </c>
     </row>
     <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A367" s="23">
+      <c r="A367" s="22">
         <v>124</v>
       </c>
       <c r="B367" s="5" t="s">
@@ -11386,7 +11386,7 @@
       </c>
     </row>
     <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A368" s="23">
+      <c r="A368" s="22">
         <v>125</v>
       </c>
       <c r="B368" s="5" t="s">
@@ -11415,7 +11415,7 @@
       </c>
     </row>
     <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A369" s="23">
+      <c r="A369" s="22">
         <v>125</v>
       </c>
       <c r="B369" s="5" t="s">
@@ -11444,7 +11444,7 @@
       </c>
     </row>
     <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A370" s="23">
+      <c r="A370" s="22">
         <v>126</v>
       </c>
       <c r="B370" s="5" t="s">
@@ -11473,7 +11473,7 @@
       </c>
     </row>
     <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A371" s="23">
+      <c r="A371" s="22">
         <v>126</v>
       </c>
       <c r="B371" s="5" t="s">
@@ -11502,7 +11502,7 @@
       </c>
     </row>
     <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A372" s="23">
+      <c r="A372" s="22">
         <v>127</v>
       </c>
       <c r="B372" s="5" t="s">
@@ -11531,7 +11531,7 @@
       </c>
     </row>
     <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A373" s="23">
+      <c r="A373" s="22">
         <v>127</v>
       </c>
       <c r="B373" s="5" t="s">
@@ -11560,7 +11560,7 @@
       </c>
     </row>
     <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A374" s="23">
+      <c r="A374" s="22">
         <v>127</v>
       </c>
       <c r="B374" s="5" t="s">
@@ -11589,7 +11589,7 @@
       </c>
     </row>
     <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A375" s="23">
+      <c r="A375" s="22">
         <v>128</v>
       </c>
       <c r="B375" s="5" t="s">
@@ -11618,7 +11618,7 @@
       </c>
     </row>
     <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A376" s="23">
+      <c r="A376" s="22">
         <v>129</v>
       </c>
       <c r="B376" s="5" t="s">
@@ -11647,7 +11647,7 @@
       </c>
     </row>
     <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A377" s="23">
+      <c r="A377" s="22">
         <v>130</v>
       </c>
       <c r="B377" s="5" t="s">
@@ -11676,7 +11676,7 @@
       </c>
     </row>
     <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A378" s="23">
+      <c r="A378" s="22">
         <v>131</v>
       </c>
       <c r="B378" s="5" t="s">
@@ -11705,7 +11705,7 @@
       </c>
     </row>
     <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A379" s="23">
+      <c r="A379" s="22">
         <v>131</v>
       </c>
       <c r="B379" s="5" t="s">
@@ -11734,7 +11734,7 @@
       </c>
     </row>
     <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A380" s="23">
+      <c r="A380" s="22">
         <v>131</v>
       </c>
       <c r="B380" s="5" t="s">
@@ -11763,7 +11763,7 @@
       </c>
     </row>
     <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A381" s="23">
+      <c r="A381" s="22">
         <v>131</v>
       </c>
       <c r="B381" s="5" t="s">
@@ -11792,7 +11792,7 @@
       </c>
     </row>
     <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A382" s="23">
+      <c r="A382" s="22">
         <v>132</v>
       </c>
       <c r="B382" s="5" t="s">
@@ -11821,7 +11821,7 @@
       </c>
     </row>
     <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A383" s="23">
+      <c r="A383" s="22">
         <v>133</v>
       </c>
       <c r="B383" s="5" t="s">
@@ -11850,7 +11850,7 @@
       </c>
     </row>
     <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A384" s="23">
+      <c r="A384" s="22">
         <v>134</v>
       </c>
       <c r="B384" s="5" t="s">
@@ -11879,7 +11879,7 @@
       </c>
     </row>
     <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A385" s="23">
+      <c r="A385" s="22">
         <v>135</v>
       </c>
       <c r="B385" s="5" t="s">
@@ -11908,7 +11908,7 @@
       </c>
     </row>
     <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A386" s="23">
+      <c r="A386" s="22">
         <v>135</v>
       </c>
       <c r="B386" s="5" t="s">
@@ -11937,7 +11937,7 @@
       </c>
     </row>
     <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A387" s="23">
+      <c r="A387" s="22">
         <v>135</v>
       </c>
       <c r="B387" s="5" t="s">
@@ -11966,7 +11966,7 @@
       </c>
     </row>
     <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A388" s="23">
+      <c r="A388" s="22">
         <v>135</v>
       </c>
       <c r="B388" s="5" t="s">
@@ -11995,7 +11995,7 @@
       </c>
     </row>
     <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A389" s="23">
+      <c r="A389" s="22">
         <v>136</v>
       </c>
       <c r="B389" s="5" t="s">
@@ -12024,7 +12024,7 @@
       </c>
     </row>
     <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A390" s="23">
+      <c r="A390" s="22">
         <v>136</v>
       </c>
       <c r="B390" s="5" t="s">
@@ -12053,7 +12053,7 @@
       </c>
     </row>
     <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A391" s="23">
+      <c r="A391" s="22">
         <v>136</v>
       </c>
       <c r="B391" s="5" t="s">
@@ -12082,7 +12082,7 @@
       </c>
     </row>
     <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A392" s="23">
+      <c r="A392" s="22">
         <v>136</v>
       </c>
       <c r="B392" s="5" t="s">
@@ -12111,7 +12111,7 @@
       </c>
     </row>
     <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A393" s="23">
+      <c r="A393" s="22">
         <v>137</v>
       </c>
       <c r="B393" s="5" t="s">
@@ -12140,7 +12140,7 @@
       </c>
     </row>
     <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A394" s="23">
+      <c r="A394" s="22">
         <v>137</v>
       </c>
       <c r="B394" s="5" t="s">
@@ -12169,7 +12169,7 @@
       </c>
     </row>
     <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A395" s="23">
+      <c r="A395" s="22">
         <v>137</v>
       </c>
       <c r="B395" s="5" t="s">
@@ -12198,7 +12198,7 @@
       </c>
     </row>
     <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A396" s="23">
+      <c r="A396" s="22">
         <v>137</v>
       </c>
       <c r="B396" s="5" t="s">
@@ -12227,7 +12227,7 @@
       </c>
     </row>
     <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A397" s="23">
+      <c r="A397" s="22">
         <v>138</v>
       </c>
       <c r="B397" s="5" t="s">
@@ -12256,7 +12256,7 @@
       </c>
     </row>
     <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A398" s="23">
+      <c r="A398" s="22">
         <v>138</v>
       </c>
       <c r="B398" s="5" t="s">
@@ -12285,7 +12285,7 @@
       </c>
     </row>
     <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A399" s="23">
+      <c r="A399" s="22">
         <v>138</v>
       </c>
       <c r="B399" s="5" t="s">
@@ -12314,7 +12314,7 @@
       </c>
     </row>
     <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A400" s="23">
+      <c r="A400" s="22">
         <v>138</v>
       </c>
       <c r="B400" s="5" t="s">
@@ -12343,7 +12343,7 @@
       </c>
     </row>
     <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A401" s="23">
+      <c r="A401" s="22">
         <v>138</v>
       </c>
       <c r="B401" s="5" t="s">
@@ -12372,7 +12372,7 @@
       </c>
     </row>
     <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A402" s="23">
+      <c r="A402" s="22">
         <v>138</v>
       </c>
       <c r="B402" s="5" t="s">
@@ -12401,7 +12401,7 @@
       </c>
     </row>
     <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A403" s="23">
+      <c r="A403" s="22">
         <v>138</v>
       </c>
       <c r="B403" s="5" t="s">
@@ -12430,7 +12430,7 @@
       </c>
     </row>
     <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A404" s="23">
+      <c r="A404" s="22">
         <v>138</v>
       </c>
       <c r="B404" s="5" t="s">
@@ -12459,7 +12459,7 @@
       </c>
     </row>
     <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A405" s="23">
+      <c r="A405" s="22">
         <v>138</v>
       </c>
       <c r="B405" s="5" t="s">
@@ -12488,7 +12488,7 @@
       </c>
     </row>
     <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A406" s="23">
+      <c r="A406" s="22">
         <v>139</v>
       </c>
       <c r="B406" s="5" t="s">
@@ -12517,7 +12517,7 @@
       </c>
     </row>
     <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A407" s="23">
+      <c r="A407" s="22">
         <v>139</v>
       </c>
       <c r="B407" s="5" t="s">
@@ -12546,7 +12546,7 @@
       </c>
     </row>
     <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A408" s="23">
+      <c r="A408" s="22">
         <v>139</v>
       </c>
       <c r="B408" s="5" t="s">
@@ -12575,7 +12575,7 @@
       </c>
     </row>
     <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A409" s="23">
+      <c r="A409" s="22">
         <v>139</v>
       </c>
       <c r="B409" s="5" t="s">
@@ -12604,7 +12604,7 @@
       </c>
     </row>
     <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A410" s="23">
+      <c r="A410" s="22">
         <v>139</v>
       </c>
       <c r="B410" s="5" t="s">
@@ -12633,7 +12633,7 @@
       </c>
     </row>
     <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A411" s="23">
+      <c r="A411" s="22">
         <v>139</v>
       </c>
       <c r="B411" s="5" t="s">
@@ -12662,7 +12662,7 @@
       </c>
     </row>
     <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A412" s="23">
+      <c r="A412" s="22">
         <v>139</v>
       </c>
       <c r="B412" s="5" t="s">
@@ -12691,7 +12691,7 @@
       </c>
     </row>
     <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A413" s="23">
+      <c r="A413" s="22">
         <v>139</v>
       </c>
       <c r="B413" s="5" t="s">
@@ -12720,7 +12720,7 @@
       </c>
     </row>
     <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A414" s="23">
+      <c r="A414" s="22">
         <v>139</v>
       </c>
       <c r="B414" s="5" t="s">
@@ -12749,7 +12749,7 @@
       </c>
     </row>
     <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A415" s="23">
+      <c r="A415" s="22">
         <v>139</v>
       </c>
       <c r="B415" s="5" t="s">
@@ -12778,7 +12778,7 @@
       </c>
     </row>
     <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A416" s="23">
+      <c r="A416" s="22">
         <v>139</v>
       </c>
       <c r="B416" s="5" t="s">
@@ -12807,7 +12807,7 @@
       </c>
     </row>
     <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A417" s="23">
+      <c r="A417" s="22">
         <v>140</v>
       </c>
       <c r="B417" s="5" t="s">
@@ -12836,7 +12836,7 @@
       </c>
     </row>
     <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A418" s="23">
+      <c r="A418" s="22">
         <v>141</v>
       </c>
       <c r="B418" s="5" t="s">
@@ -12865,7 +12865,7 @@
       </c>
     </row>
     <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A419" s="23">
+      <c r="A419" s="22">
         <v>141</v>
       </c>
       <c r="B419" s="5" t="s">
@@ -12894,7 +12894,7 @@
       </c>
     </row>
     <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A420" s="23">
+      <c r="A420" s="22">
         <v>142</v>
       </c>
       <c r="B420" s="5" t="s">
@@ -12923,7 +12923,7 @@
       </c>
     </row>
     <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A421" s="23">
+      <c r="A421" s="22">
         <v>142</v>
       </c>
       <c r="B421" s="5" t="s">
@@ -12952,7 +12952,7 @@
       </c>
     </row>
     <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A422" s="23">
+      <c r="A422" s="22">
         <v>142</v>
       </c>
       <c r="B422" s="5" t="s">
@@ -12981,7 +12981,7 @@
       </c>
     </row>
     <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A423" s="23">
+      <c r="A423" s="22">
         <v>143</v>
       </c>
       <c r="B423" s="13" t="s">
@@ -13010,7 +13010,7 @@
       </c>
     </row>
     <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A424" s="23">
+      <c r="A424" s="22">
         <v>144</v>
       </c>
       <c r="B424" s="13" t="s">
@@ -13035,11 +13035,11 @@
         <v>3</v>
       </c>
       <c r="I424" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A425" s="23">
+      <c r="A425" s="22">
         <v>144</v>
       </c>
       <c r="B425" s="13" t="s">
@@ -13068,7 +13068,7 @@
       </c>
     </row>
     <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A426" s="23">
+      <c r="A426" s="22">
         <v>145</v>
       </c>
       <c r="B426" s="13" t="s">
@@ -13089,7 +13089,7 @@
       <c r="G426" s="6">
         <v>0</v>
       </c>
-      <c r="H426" s="15">
+      <c r="H426" s="28">
         <v>3</v>
       </c>
       <c r="I426" s="13">
@@ -13097,7 +13097,7 @@
       </c>
     </row>
     <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A427" s="23">
+      <c r="A427" s="22">
         <v>146</v>
       </c>
       <c r="B427" s="13" t="s">
@@ -13118,15 +13118,15 @@
       <c r="G427" s="6">
         <v>0</v>
       </c>
-      <c r="H427" s="17">
+      <c r="H427" s="28">
         <v>3</v>
       </c>
       <c r="I427" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A428" s="23">
+      <c r="A428" s="22">
         <v>146</v>
       </c>
       <c r="B428" s="13" t="s">
@@ -13147,15 +13147,15 @@
       <c r="G428" s="6">
         <v>0</v>
       </c>
-      <c r="H428" s="15">
+      <c r="H428" s="28">
         <v>3</v>
       </c>
       <c r="I428" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A429" s="23">
+      <c r="A429" s="22">
         <v>146</v>
       </c>
       <c r="B429" s="13" t="s">
@@ -13176,15 +13176,15 @@
       <c r="G429" s="6">
         <v>0</v>
       </c>
-      <c r="H429" s="17">
+      <c r="H429" s="28">
         <v>3</v>
       </c>
       <c r="I429" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A430" s="23">
+      <c r="A430" s="22">
         <v>146</v>
       </c>
       <c r="B430" s="13" t="s">
@@ -13205,7 +13205,7 @@
       <c r="G430" s="6">
         <v>0</v>
       </c>
-      <c r="H430" s="17">
+      <c r="H430" s="28">
         <v>3</v>
       </c>
       <c r="I430" s="13">
@@ -13213,7 +13213,7 @@
       </c>
     </row>
     <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A431" s="23">
+      <c r="A431" s="22">
         <v>147</v>
       </c>
       <c r="B431" s="13" t="s">
@@ -13234,7 +13234,7 @@
       <c r="G431" s="6">
         <v>0</v>
       </c>
-      <c r="H431" s="15">
+      <c r="H431" s="28">
         <v>3</v>
       </c>
       <c r="I431" s="13">
@@ -13242,7 +13242,7 @@
       </c>
     </row>
     <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A432" s="23">
+      <c r="A432" s="22">
         <v>148</v>
       </c>
       <c r="B432" s="13" t="s">
@@ -13263,7 +13263,7 @@
       <c r="G432" s="6">
         <v>0</v>
       </c>
-      <c r="H432" s="15">
+      <c r="H432" s="28">
         <v>3</v>
       </c>
       <c r="I432" s="13">
@@ -13271,7 +13271,7 @@
       </c>
     </row>
     <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A433" s="23">
+      <c r="A433" s="22">
         <v>149</v>
       </c>
       <c r="B433" s="13" t="s">
@@ -13300,7 +13300,7 @@
       </c>
     </row>
     <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A434" s="23">
+      <c r="A434" s="22">
         <v>150</v>
       </c>
       <c r="B434" s="13" t="s">
@@ -13329,7 +13329,7 @@
       </c>
     </row>
     <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A435" s="23">
+      <c r="A435" s="22">
         <v>151</v>
       </c>
       <c r="B435" s="13" t="s">
@@ -13358,7 +13358,7 @@
       </c>
     </row>
     <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A436" s="23">
+      <c r="A436" s="22">
         <v>152</v>
       </c>
       <c r="B436" s="13" t="s">
@@ -13387,7 +13387,7 @@
       </c>
     </row>
     <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="23">
+      <c r="A437" s="22">
         <v>153</v>
       </c>
       <c r="B437" s="13" t="s">
@@ -13416,7 +13416,7 @@
       </c>
     </row>
     <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="23">
+      <c r="A438" s="22">
         <v>154</v>
       </c>
       <c r="B438" s="13" t="s">
@@ -13445,7 +13445,7 @@
       </c>
     </row>
     <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A439" s="23">
+      <c r="A439" s="22">
         <v>155</v>
       </c>
       <c r="B439" s="13" t="s">
@@ -13474,7 +13474,7 @@
       </c>
     </row>
     <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A440" s="23">
+      <c r="A440" s="22">
         <v>156</v>
       </c>
       <c r="B440" s="13" t="s">
@@ -13503,7 +13503,7 @@
       </c>
     </row>
     <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A441" s="23">
+      <c r="A441" s="22">
         <v>157</v>
       </c>
       <c r="B441" s="13" t="s">
@@ -13528,11 +13528,11 @@
         <v>3</v>
       </c>
       <c r="I441" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A442" s="23">
+      <c r="A442" s="22">
         <v>157</v>
       </c>
       <c r="B442" s="13" t="s">
@@ -13553,7 +13553,7 @@
       <c r="G442" s="6">
         <v>0</v>
       </c>
-      <c r="H442" s="17">
+      <c r="H442" s="28">
         <v>3</v>
       </c>
       <c r="I442" s="13">
@@ -13561,7 +13561,7 @@
       </c>
     </row>
     <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A443" s="23">
+      <c r="A443" s="22">
         <v>158</v>
       </c>
       <c r="B443" s="13" t="s">
@@ -13586,11 +13586,11 @@
         <v>3</v>
       </c>
       <c r="I443" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A444" s="23">
+      <c r="A444" s="22">
         <v>158</v>
       </c>
       <c r="B444" s="13" t="s">
@@ -13619,7 +13619,7 @@
       </c>
     </row>
     <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A445" s="23">
+      <c r="A445" s="22">
         <v>159</v>
       </c>
       <c r="B445" s="13" t="s">
@@ -13648,7 +13648,7 @@
       </c>
     </row>
     <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A446" s="23">
+      <c r="A446" s="22">
         <v>160</v>
       </c>
       <c r="B446" s="13" t="s">
@@ -13677,7 +13677,7 @@
       </c>
     </row>
     <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A447" s="23">
+      <c r="A447" s="22">
         <v>161</v>
       </c>
       <c r="B447" s="13" t="s">
@@ -13706,7 +13706,7 @@
       </c>
     </row>
     <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="23">
+      <c r="A448" s="22">
         <v>162</v>
       </c>
       <c r="B448" s="13" t="s">
@@ -13731,11 +13731,11 @@
         <v>3</v>
       </c>
       <c r="I448" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A449" s="23">
+      <c r="A449" s="22">
         <v>162</v>
       </c>
       <c r="B449" s="13" t="s">
@@ -13760,11 +13760,11 @@
         <v>3</v>
       </c>
       <c r="I449" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A450" s="23">
+      <c r="A450" s="22">
         <v>162</v>
       </c>
       <c r="B450" s="13" t="s">
@@ -13793,7 +13793,7 @@
       </c>
     </row>
     <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A451" s="23">
+      <c r="A451" s="22">
         <v>163</v>
       </c>
       <c r="B451" s="13" t="s">
@@ -13818,11 +13818,11 @@
         <v>3</v>
       </c>
       <c r="I451" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="23">
+      <c r="A452" s="22">
         <v>163</v>
       </c>
       <c r="B452" s="13" t="s">
@@ -13851,7 +13851,7 @@
       </c>
     </row>
     <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A453" s="23">
+      <c r="A453" s="22">
         <v>164</v>
       </c>
       <c r="B453" s="13" t="s">
@@ -13876,11 +13876,11 @@
         <v>3</v>
       </c>
       <c r="I453" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="23">
+      <c r="A454" s="22">
         <v>164</v>
       </c>
       <c r="B454" s="13" t="s">
@@ -13909,7 +13909,7 @@
       </c>
     </row>
     <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A455" s="23">
+      <c r="A455" s="22">
         <v>165</v>
       </c>
       <c r="B455" s="13" t="s">
@@ -13938,7 +13938,7 @@
       </c>
     </row>
     <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="23">
+      <c r="A456" s="22">
         <v>166</v>
       </c>
       <c r="B456" s="13" t="s">
@@ -13963,11 +13963,11 @@
         <v>3</v>
       </c>
       <c r="I456" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A457" s="23">
+      <c r="A457" s="22">
         <v>166</v>
       </c>
       <c r="B457" s="13" t="s">
@@ -13996,7 +13996,7 @@
       </c>
     </row>
     <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="23">
+      <c r="A458" s="22">
         <v>167</v>
       </c>
       <c r="B458" s="13" t="s">
@@ -14025,7 +14025,7 @@
       </c>
     </row>
     <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A459" s="23">
+      <c r="A459" s="22">
         <v>168</v>
       </c>
       <c r="B459" s="13" t="s">
@@ -14054,7 +14054,7 @@
       </c>
     </row>
     <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="23">
+      <c r="A460" s="22">
         <v>169</v>
       </c>
       <c r="B460" s="13" t="s">
@@ -14083,7 +14083,7 @@
       </c>
     </row>
     <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="23">
+      <c r="A461" s="22">
         <v>170</v>
       </c>
       <c r="B461" s="13" t="s">
@@ -14104,7 +14104,7 @@
       <c r="G461" s="6">
         <v>0</v>
       </c>
-      <c r="H461" s="15">
+      <c r="H461" s="28">
         <v>3</v>
       </c>
       <c r="I461" s="13">
@@ -14112,7 +14112,7 @@
       </c>
     </row>
     <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A462" s="23">
+      <c r="A462" s="22">
         <v>171</v>
       </c>
       <c r="B462" s="13" t="s">
@@ -14133,15 +14133,15 @@
       <c r="G462" s="6">
         <v>0</v>
       </c>
-      <c r="H462" s="15">
+      <c r="H462" s="28">
         <v>3</v>
       </c>
       <c r="I462" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A463" s="23">
+      <c r="A463" s="22">
         <v>171</v>
       </c>
       <c r="B463" s="13" t="s">
@@ -14162,7 +14162,7 @@
       <c r="G463" s="6">
         <v>0</v>
       </c>
-      <c r="H463" s="15">
+      <c r="H463" s="28">
         <v>3</v>
       </c>
       <c r="I463" s="13">
@@ -14170,7 +14170,7 @@
       </c>
     </row>
     <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A464" s="23">
+      <c r="A464" s="22">
         <v>172</v>
       </c>
       <c r="B464" s="13" t="s">
@@ -14191,7 +14191,7 @@
       <c r="G464" s="6">
         <v>0</v>
       </c>
-      <c r="H464" s="15">
+      <c r="H464" s="28">
         <v>3</v>
       </c>
       <c r="I464" s="13">
@@ -14199,7 +14199,7 @@
       </c>
     </row>
     <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A465" s="23">
+      <c r="A465" s="22">
         <v>173</v>
       </c>
       <c r="B465" s="13" t="s">
@@ -14220,7 +14220,7 @@
       <c r="G465" s="6">
         <v>0</v>
       </c>
-      <c r="H465" s="15">
+      <c r="H465" s="28">
         <v>3</v>
       </c>
       <c r="I465" s="13">
@@ -14228,7 +14228,7 @@
       </c>
     </row>
     <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A466" s="23">
+      <c r="A466" s="22">
         <v>174</v>
       </c>
       <c r="B466" s="13" t="s">
@@ -14249,7 +14249,7 @@
       <c r="G466" s="6">
         <v>0</v>
       </c>
-      <c r="H466" s="15">
+      <c r="H466" s="28">
         <v>3</v>
       </c>
       <c r="I466" s="13">
@@ -14257,7 +14257,7 @@
       </c>
     </row>
     <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="23">
+      <c r="A467" s="22">
         <v>175</v>
       </c>
       <c r="B467" s="13" t="s">
@@ -14278,7 +14278,7 @@
       <c r="G467" s="6">
         <v>0</v>
       </c>
-      <c r="H467" s="15">
+      <c r="H467" s="28">
         <v>3</v>
       </c>
       <c r="I467" s="13">
@@ -14286,7 +14286,7 @@
       </c>
     </row>
     <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="23">
+      <c r="A468" s="22">
         <v>176</v>
       </c>
       <c r="B468" s="13" t="s">
@@ -14307,15 +14307,15 @@
       <c r="G468" s="6">
         <v>0</v>
       </c>
-      <c r="H468" s="15">
+      <c r="H468" s="28">
         <v>3</v>
       </c>
       <c r="I468" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A469" s="23">
+      <c r="A469" s="22">
         <v>176</v>
       </c>
       <c r="B469" s="13" t="s">
@@ -14336,7 +14336,7 @@
       <c r="G469" s="6">
         <v>0</v>
       </c>
-      <c r="H469" s="17">
+      <c r="H469" s="28">
         <v>3</v>
       </c>
       <c r="I469" s="13">
@@ -14344,7 +14344,7 @@
       </c>
     </row>
     <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="23">
+      <c r="A470" s="22">
         <v>177</v>
       </c>
       <c r="B470" s="13" t="s">
@@ -14365,7 +14365,7 @@
       <c r="G470" s="6">
         <v>0</v>
       </c>
-      <c r="H470" s="15">
+      <c r="H470" s="28">
         <v>3</v>
       </c>
       <c r="I470" s="13">
@@ -14373,7 +14373,7 @@
       </c>
     </row>
     <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A471" s="23">
+      <c r="A471" s="22">
         <v>178</v>
       </c>
       <c r="B471" s="13" t="s">
@@ -14394,7 +14394,7 @@
       <c r="G471" s="6">
         <v>0</v>
       </c>
-      <c r="H471" s="15">
+      <c r="H471" s="28">
         <v>3</v>
       </c>
       <c r="I471" s="13">
@@ -14402,7 +14402,7 @@
       </c>
     </row>
     <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A472" s="23">
+      <c r="A472" s="22">
         <v>179</v>
       </c>
       <c r="B472" s="13" t="s">
@@ -14423,15 +14423,15 @@
       <c r="G472" s="6">
         <v>0</v>
       </c>
-      <c r="H472" s="15">
+      <c r="H472" s="28">
         <v>3</v>
       </c>
       <c r="I472" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A473" s="23">
+      <c r="A473" s="22">
         <v>179</v>
       </c>
       <c r="B473" s="13" t="s">
@@ -14452,7 +14452,7 @@
       <c r="G473" s="6">
         <v>0</v>
       </c>
-      <c r="H473" s="17">
+      <c r="H473" s="28">
         <v>3</v>
       </c>
       <c r="I473" s="13">
@@ -14460,7 +14460,7 @@
       </c>
     </row>
     <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A474" s="23">
+      <c r="A474" s="22">
         <v>180</v>
       </c>
       <c r="B474" s="13" t="s">
@@ -14481,7 +14481,7 @@
       <c r="G474" s="6">
         <v>0</v>
       </c>
-      <c r="H474" s="15">
+      <c r="H474" s="28">
         <v>3</v>
       </c>
       <c r="I474" s="13">
@@ -14489,7 +14489,7 @@
       </c>
     </row>
     <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A475" s="23">
+      <c r="A475" s="22">
         <v>181</v>
       </c>
       <c r="B475" s="13" t="s">
@@ -14510,15 +14510,15 @@
       <c r="G475" s="6">
         <v>0</v>
       </c>
-      <c r="H475" s="15">
+      <c r="H475" s="28">
         <v>3</v>
       </c>
       <c r="I475" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A476" s="23">
+      <c r="A476" s="22">
         <v>181</v>
       </c>
       <c r="B476" s="13" t="s">
@@ -14539,7 +14539,7 @@
       <c r="G476" s="6">
         <v>0</v>
       </c>
-      <c r="H476" s="15">
+      <c r="H476" s="28">
         <v>3</v>
       </c>
       <c r="I476" s="13">
@@ -14547,7 +14547,7 @@
       </c>
     </row>
     <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A477" s="23">
+      <c r="A477" s="22">
         <v>182</v>
       </c>
       <c r="B477" s="13" t="s">
@@ -14576,7 +14576,7 @@
       </c>
     </row>
     <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="23">
+      <c r="A478" s="22">
         <v>183</v>
       </c>
       <c r="B478" s="13" t="s">
@@ -14605,7 +14605,7 @@
       </c>
     </row>
     <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="23">
+      <c r="A479" s="22">
         <v>184</v>
       </c>
       <c r="B479" s="13" t="s">
@@ -14634,7 +14634,7 @@
       </c>
     </row>
     <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="23">
+      <c r="A480" s="22">
         <v>185</v>
       </c>
       <c r="B480" s="13" t="s">
@@ -14659,11 +14659,11 @@
         <v>3</v>
       </c>
       <c r="I480" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="23">
+      <c r="A481" s="22">
         <v>185</v>
       </c>
       <c r="B481" s="13" t="s">
@@ -14692,7 +14692,7 @@
       </c>
     </row>
     <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="23">
+      <c r="A482" s="22">
         <v>186</v>
       </c>
       <c r="B482" s="13" t="s">
@@ -14721,7 +14721,7 @@
       </c>
     </row>
     <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="23">
+      <c r="A483" s="22">
         <v>187</v>
       </c>
       <c r="B483" s="13" t="s">
@@ -14750,7 +14750,7 @@
       </c>
     </row>
     <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="23">
+      <c r="A484" s="22">
         <v>188</v>
       </c>
       <c r="B484" s="13" t="s">
@@ -14775,11 +14775,11 @@
         <v>3</v>
       </c>
       <c r="I484" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A485" s="23">
+      <c r="A485" s="22">
         <v>188</v>
       </c>
       <c r="B485" s="13" t="s">
@@ -14829,13 +14829,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15080,10 +15080,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15129,10 +15129,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>23</v>
       </c>
     </row>
